--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2FC09C-EA6F-4DDC-A9AC-6B8C84C5FCF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDFB544-81AE-48B5-984D-37F0352B7A5F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semana 5 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
-    <sheet name="Semana 1 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
+    <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
+    <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -4015,6 +4015,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4215,22 +4230,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4247,21 +4264,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDFB544-81AE-48B5-984D-37F0352B7A5F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB7E774-EF83-4A72-B478-1DBB1CA9DF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId3"/>
+    <sheet name="Semana 2 - 14 al 18 de Oct  " sheetId="26" r:id="rId3"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="117">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -415,12 +416,24 @@
   <si>
     <t xml:space="preserve">Apoyo en tarea operativas según asignación </t>
   </si>
+  <si>
+    <t xml:space="preserve">Alexander </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abuso de Bonos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyo en tareas operativas según asignación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyo aprobación de retiros </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,7 +642,417 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="122">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1771,24 +2194,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AC30FF-4C9E-4211-B41D-FEC83E8B88B1}">
   <dimension ref="B3:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.09765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.69921875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.59765625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.59765625" style="2"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
@@ -1807,7 +2230,7 @@
       </c>
       <c r="L3" s="19"/>
     </row>
-    <row r="4" spans="2:12" ht="14.4">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1834,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="14.4">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1860,7 +2283,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.4">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
@@ -1886,7 +2309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.4">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -1912,7 +2335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.4">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
@@ -1938,7 +2361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.4">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
@@ -1964,7 +2387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="14.4">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
@@ -1990,7 +2413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="14.4">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
@@ -2016,7 +2439,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="14.4">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>29</v>
       </c>
@@ -2042,7 +2465,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="14.4">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
@@ -2068,7 +2491,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="14.4">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>102</v>
       </c>
@@ -2095,7 +2518,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="14.4">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
         <v>104</v>
       </c>
@@ -2122,7 +2545,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="27.6">
+    <row r="16" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>95</v>
       </c>
@@ -2148,7 +2571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="14.4">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
@@ -2170,7 +2593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="14.4">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E18" s="6" t="s">
         <v>25</v>
       </c>
@@ -2191,7 +2614,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="19" t="s">
         <v>24</v>
       </c>
@@ -2203,7 +2626,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="14.4">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -2225,7 +2648,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="2:12" ht="27.6">
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -2251,7 +2674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="14.4">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="18"/>
       <c r="F22" s="2"/>
       <c r="H22" s="11" t="s">
@@ -2267,7 +2690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="14.4">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E23" s="19" t="s">
         <v>89</v>
       </c>
@@ -2285,7 +2708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="14.4">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="19" t="s">
         <v>36</v>
       </c>
@@ -2309,7 +2732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="14.4">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
@@ -2335,7 +2758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="14.4">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
@@ -2361,7 +2784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="14.4">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="16" t="s">
         <v>34</v>
       </c>
@@ -2387,7 +2810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="14.4">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>77</v>
       </c>
@@ -2413,7 +2836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="14.4">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>22</v>
       </c>
@@ -2433,7 +2856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="14.4">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
@@ -2453,7 +2876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="14.4">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>40</v>
       </c>
@@ -2473,7 +2896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="14.4">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
@@ -2494,7 +2917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:12" ht="14.4">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>78</v>
       </c>
@@ -2516,7 +2939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -2525,7 +2948,7 @@
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:12">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -2542,7 +2965,7 @@
       </c>
       <c r="L35" s="19"/>
     </row>
-    <row r="36" spans="2:12" ht="14.4">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>42</v>
       </c>
@@ -2563,7 +2986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>12</v>
@@ -2578,7 +3001,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>16</v>
@@ -2593,7 +3016,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>41</v>
@@ -2608,7 +3031,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>22</v>
@@ -2623,7 +3046,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="2:12">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D41"/>
       <c r="H41" s="6" t="s">
         <v>21</v>
@@ -2638,7 +3061,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:12">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D42"/>
     </row>
   </sheetData>
@@ -2657,124 +3080,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="78" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="77" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="76" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="75" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="73" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="72" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="64" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="62" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="52" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="51" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="50" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="48" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="47" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="46" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="45" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="44" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="42" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="41" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2783,24 +3206,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D300C407-A034-411B-B7F2-D7830F6D8BD1}">
   <dimension ref="B2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.09765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.8984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.59765625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.296875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.59765625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.59765625" style="2"/>
+    <col min="4" max="4" width="11.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -2819,7 +3242,7 @@
       </c>
       <c r="L2" s="19"/>
     </row>
-    <row r="3" spans="2:12" ht="14.4">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2846,7 +3269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.4">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -2872,7 +3295,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="14.4">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -2898,7 +3321,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.4">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -2924,7 +3347,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.4">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -2950,7 +3373,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.4">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2976,7 +3399,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.4">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -3002,7 +3425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="14.4">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -3028,7 +3451,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="14.4">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -3054,7 +3477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="14.4">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -3080,7 +3503,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="14.4">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>94</v>
       </c>
@@ -3107,7 +3530,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="14.4">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
@@ -3134,7 +3557,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="14.4">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -3160,7 +3583,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.4">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -3182,7 +3605,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="14.4">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -3203,7 +3626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="19" t="s">
         <v>24</v>
       </c>
@@ -3215,7 +3638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="14.4">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -3237,7 +3660,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" spans="2:12" ht="27.6">
+    <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -3263,7 +3686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>111</v>
       </c>
@@ -3289,7 +3712,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>112</v>
       </c>
@@ -3310,7 +3733,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="18"/>
       <c r="E23" s="18"/>
       <c r="H23" s="11" t="s">
@@ -3326,7 +3749,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="F24" s="2"/>
       <c r="H24" s="11" t="s">
@@ -3342,7 +3765,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
       <c r="E25" s="19" t="s">
         <v>89</v>
@@ -3361,7 +3784,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="14.4">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="19" t="s">
         <v>36</v>
       </c>
@@ -3385,7 +3808,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="14.4">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>4</v>
       </c>
@@ -3411,7 +3834,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>26</v>
       </c>
@@ -3437,7 +3860,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>34</v>
       </c>
@@ -3463,7 +3886,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>77</v>
       </c>
@@ -3489,7 +3912,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
@@ -3510,7 +3933,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
@@ -3532,7 +3955,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>40</v>
       </c>
@@ -3541,7 +3964,7 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -3558,7 +3981,7 @@
       </c>
       <c r="L34" s="19"/>
     </row>
-    <row r="35" spans="2:12" ht="14.4">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -3579,7 +4002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -3594,7 +4017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -3609,7 +4032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>41</v>
@@ -3624,7 +4047,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -3639,7 +4062,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>21</v>
@@ -3654,7 +4077,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="2:12">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D41"/>
     </row>
   </sheetData>
@@ -3673,142 +4096,1179 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="36" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975FC815-190A-423D-8B89-8859EE2B07D5}">
+  <dimension ref="B2:L41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="K2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="K19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="H21" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="H22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="18"/>
+      <c r="F23" s="2"/>
+      <c r="H23" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="E24" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="H24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="18"/>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="H32" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="21"/>
+      <c r="K34" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+      <c r="H35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36"/>
+      <c r="H36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+      <c r="H37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+      <c r="H38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+      <c r="H39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+      <c r="H40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D41"/>
+      <c r="H41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="f2VEDGTmKAD6fAnuA+OQ/f5F473fmL1PnHuX4kDzgTWHB0kJVIHUABju1s9ko3FFq0uy0/WFDoYt7mrLKYnh0g==" saltValue="4yJYYj5jH9UDpg1RyyT3rg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="11">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B12">
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="36" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B11">
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B22:B25">
+    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B10">
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33 B9">
+    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K26:K27">
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K31">
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39">
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K40">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.19921875" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>48</v>
       </c>
@@ -3816,7 +5276,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="27.6">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -3824,7 +5284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="27.6">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
@@ -3832,7 +5292,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="27.6">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
@@ -3840,7 +5300,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="27.6">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>21</v>
       </c>
@@ -3848,7 +5308,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="41.4">
+    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -3856,7 +5316,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
@@ -3864,7 +5324,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="55.2">
+    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -3872,7 +5332,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27.6">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>58</v>
       </c>
@@ -3880,7 +5340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>20</v>
       </c>
@@ -3888,7 +5348,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="41.4">
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
@@ -3896,7 +5356,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="41.4">
+    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -3904,7 +5364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="41.4">
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>25</v>
       </c>
@@ -3912,7 +5372,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="27.6">
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -3920,7 +5380,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="96.6">
+    <row r="15" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
@@ -3928,7 +5388,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="96.6">
+    <row r="16" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>39</v>
       </c>
@@ -3936,7 +5396,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="41.4">
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
@@ -3944,7 +5404,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="27.6">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>29</v>
       </c>
@@ -3952,7 +5412,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="27.6">
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>40</v>
       </c>
@@ -3960,7 +5420,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="138">
+    <row r="20" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
@@ -3968,7 +5428,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="55.2">
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>33</v>
       </c>
@@ -3976,7 +5436,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="41.4">
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>41</v>
       </c>
@@ -3984,7 +5444,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="96.6">
+    <row r="23" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>47</v>
       </c>
@@ -3992,7 +5452,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="55.2">
+    <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>19</v>
       </c>
@@ -4000,7 +5460,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="41.4">
+    <row r="25" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>35</v>
       </c>
@@ -4015,21 +5475,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4230,24 +5675,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4264,4 +5707,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB7E774-EF83-4A72-B478-1DBB1CA9DF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E745CF6-6B5B-4FDE-BA81-4949A9A84C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 2 - 14 al 18 de Oct  " sheetId="26" r:id="rId3"/>
+    <sheet name="Semana 2 - 12 al 13 Oct" sheetId="27" r:id="rId3"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="115">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -418,12 +418,6 @@
   </si>
   <si>
     <t xml:space="preserve">Alexander </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abuso de Bonos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyo en tareas operativas según asignación </t>
   </si>
   <si>
     <t xml:space="preserve">Apoyo aprobación de retiros </t>
@@ -642,217 +636,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="122">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="101">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3080,124 +2864,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4096,153 +3880,148 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975FC815-190A-423D-8B89-8859EE2B07D5}">
-  <dimension ref="B2:L41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC7BEC3-866A-41A2-A53C-81932A25FCAC}">
+  <dimension ref="B2:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -4252,16 +4031,8 @@
         <v>1</v>
       </c>
       <c r="F2" s="19"/>
-      <c r="H2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="19"/>
-      <c r="K2" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="19"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -4275,20 +4046,8 @@
       <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4301,25 +4060,13 @@
       <c r="F4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>10</v>
@@ -4327,20 +4074,8 @@
       <c r="F5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -4353,25 +4088,13 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>17</v>
@@ -4379,20 +4102,8 @@
       <c r="F7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -4405,25 +4116,13 @@
       <c r="F8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>20</v>
@@ -4431,20 +4130,8 @@
       <c r="F9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -4457,25 +4144,13 @@
       <c r="F10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
@@ -4483,20 +4158,8 @@
       <c r="F11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -4509,25 +4172,13 @@
       <c r="F12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="6" t="s">
@@ -4536,20 +4187,8 @@
       <c r="F13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -4563,25 +4202,13 @@
       <c r="F14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>110</v>
@@ -4589,20 +4216,8 @@
       <c r="F15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -4610,42 +4225,16 @@
         <v>38</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="19" t="s">
         <v>24</v>
       </c>
@@ -4657,7 +4246,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -4670,16 +4259,8 @@
       <c r="F19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H19" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="19"/>
-      <c r="K19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="19"/>
-    </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -4692,147 +4273,68 @@
       <c r="F20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I20" s="3" t="s">
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="18"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="18"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="H21" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="H22" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="18"/>
-      <c r="F23" s="2"/>
-      <c r="H23" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="18"/>
       <c r="E24" s="19" t="s">
         <v>89</v>
       </c>
       <c r="F24" s="19"/>
-      <c r="H24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="18"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="19"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="E26" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>5</v>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
@@ -4840,22 +4342,10 @@
       <c r="F27" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="8" t="s">
-        <v>26</v>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>14</v>
@@ -4866,22 +4356,10 @@
       <c r="F28" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H28" s="11" t="s">
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
@@ -4892,368 +4370,139 @@
       <c r="F29" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="5" t="s">
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="6" t="s">
-        <v>22</v>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="6" t="s">
-        <v>23</v>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D32"/>
-      <c r="H32" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B34" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>8</v>
-      </c>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D34"/>
-      <c r="H34" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I34" s="21"/>
-      <c r="K34" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="L34" s="19"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D35"/>
-      <c r="H35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>43</v>
-      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D36"/>
-      <c r="H36" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D37"/>
-      <c r="H37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
-      <c r="H38" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
-      <c r="H39" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D40"/>
-      <c r="H40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D41"/>
-      <c r="H41" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>113</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f2VEDGTmKAD6fAnuA+OQ/f5F473fmL1PnHuX4kDzgTWHB0kJVIHUABju1s9ko3FFq0uy0/WFDoYt7mrLKYnh0g==" saltValue="4yJYYj5jH9UDpg1RyyT3rg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="11">
+  <sheetProtection algorithmName="SHA-512" hashValue="g7PpCqarTdIHkTzAN9LPec5oCff4N7ORiNvQ6U2ufJOJceU4bPzKoy1cTMLeSq7D9+9tBTK8APT5et/nnJUEDQ==" saltValue="pT+Z8MdS8aGBH6wqRKRECA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="5">
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="36" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25 B11">
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B21:B22">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B10">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B9">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5475,6 +4724,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -5675,22 +4939,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5707,21 +4973,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E745CF6-6B5B-4FDE-BA81-4949A9A84C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28C021B-8DE3-4FFF-9874-56C7098C7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 2 - 12 al 13 Oct" sheetId="27" r:id="rId3"/>
+    <sheet name="Semana 3 - 12 al 13 Oct" sheetId="27" r:id="rId3"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -4724,21 +4724,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4939,24 +4924,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4973,4 +4956,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28C021B-8DE3-4FFF-9874-56C7098C7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F18FE9-DADF-43F2-B25F-38B18E43F536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
     <sheet name="Semana 3 - 12 al 13 Oct" sheetId="27" r:id="rId3"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
+    <sheet name="Semana 4 - 14 al 18 de Oct  " sheetId="28" r:id="rId4"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -421,6 +422,15 @@
   </si>
   <si>
     <t xml:space="preserve">Apoyo aprobación de retiros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizacion Flujo CRM dia vencido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abuso de Bonos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyo en tareas operativas según asignación </t>
   </si>
 </sst>
 </file>
@@ -571,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,11 +642,427 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="101">
+  <dxfs count="142">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2864,124 +3290,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="100" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="99" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="98" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="97" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="96" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="95" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="93" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="92" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="91" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="90" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="89" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="87" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="85" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="84" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="83" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="82" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="81" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="78" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="72" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="71" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="70" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="69" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="67" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="66" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="65" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="64" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="63" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="61" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3880,127 +4306,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="58" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="56" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="54" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="53" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="51" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="44" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="38" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="37" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="35" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="33" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="31" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="29" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="27" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="26" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4445,70 +4871,1157 @@
     <mergeCell ref="B18:C18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19CBA288-5685-457A-944C-50C7B2C8074B}">
+  <dimension ref="B2:L45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="K2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="H21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="19"/>
+      <c r="K21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="19"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="H22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="H23" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="E24" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="H24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="18"/>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="H32" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+      <c r="H33" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+      <c r="H36" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="21"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37"/>
+      <c r="H37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+      <c r="H38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+      <c r="H39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+      <c r="H40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K45" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K21:L21"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17 B12">
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29 B11">
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B23:B26">
+    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B9">
+    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:H29">
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H41">
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H42">
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27">
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:K29">
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33">
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K42">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4724,6 +6237,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -4924,22 +6452,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4956,21 +6486,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F18FE9-DADF-43F2-B25F-38B18E43F536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 3 - 12 al 13 Oct" sheetId="27" r:id="rId3"/>
-    <sheet name="Semana 4 - 14 al 18 de Oct  " sheetId="28" r:id="rId4"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
+    <sheet name="Semana 3 - 14 al 18 de Oct  " sheetId="28" r:id="rId3"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -633,6 +632,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -642,217 +647,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="142">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="122">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2422,23 +2221,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="H3" s="19" t="s">
+      <c r="F3" s="21"/>
+      <c r="H3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="19"/>
-      <c r="K3" s="19" t="s">
+      <c r="I3" s="21"/>
+      <c r="K3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="19"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -2825,10 +2624,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="21"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
@@ -2849,14 +2648,14 @@
       <c r="F20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="19"/>
-      <c r="K20" s="19" t="s">
+      <c r="I20" s="21"/>
+      <c r="K20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="19"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
@@ -2901,10 +2700,10 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="19"/>
+      <c r="F23" s="21"/>
       <c r="H23" s="11" t="s">
         <v>16</v>
       </c>
@@ -2919,10 +2718,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="21"/>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
@@ -3166,14 +2965,14 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="21"/>
-      <c r="K35" s="19" t="s">
+      <c r="I35" s="23"/>
+      <c r="K35" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="19"/>
+      <c r="L35" s="21"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
@@ -3290,124 +3089,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="141" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="140" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="139" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="138" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="137" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="136" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="135" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="134" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="133" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="132" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="131" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="130" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="129" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="128" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="127" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="126" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="125" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="124" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="123" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="122" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="121" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="120" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="119" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="118" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="117" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="116" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="115" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="114" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="113" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="112" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="111" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="110" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="109" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="108" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="107" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="106" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="105" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="104" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="103" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="102" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3434,23 +3233,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="H2" s="19" t="s">
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="K2" s="19" t="s">
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
@@ -3837,10 +3636,10 @@
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="21"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -3861,14 +3660,14 @@
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="19"/>
-      <c r="K19" s="19" t="s">
+      <c r="I19" s="21"/>
+      <c r="K19" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="19"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -3977,10 +3776,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="19"/>
+      <c r="F25" s="21"/>
       <c r="H25" s="11" t="s">
         <v>20</v>
       </c>
@@ -3995,10 +3794,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="19"/>
+      <c r="C26" s="21"/>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
@@ -4182,14 +3981,14 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="K34" s="19" t="s">
+      <c r="I34" s="23"/>
+      <c r="K34" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="19"/>
+      <c r="L34" s="21"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
@@ -4306,635 +4105,133 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="101" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="100" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="99" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="98" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="97" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="96" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="95" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="94" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="93" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="92" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="91" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="90" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="89" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="88" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="87" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="85" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="84" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="83" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="82" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="81" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="80" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="79" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="78" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="72" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="71" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="70" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="69" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="68" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="67" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="66" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="64" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="62" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="61" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC7BEC3-866A-41A2-A53C-81932A25FCAC}">
-  <dimension ref="B2:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="E16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="E18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="18"/>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="18"/>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D41"/>
-    </row>
-  </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="g7PpCqarTdIHkTzAN9LPec5oCff4N7ORiNvQ6U2ufJOJceU4bPzKoy1cTMLeSq7D9+9tBTK8APT5et/nnJUEDQ==" saltValue="pT+Z8MdS8aGBH6wqRKRECA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="5">
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B18:C18"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="60" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="57" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="56" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="55" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="54" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="53" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="49" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="48" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="46" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="45" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="44" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="42" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19CBA288-5685-457A-944C-50C7B2C8074B}">
   <dimension ref="B2:L45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4955,23 +4252,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="H2" s="19" t="s">
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="K2" s="19" t="s">
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
@@ -5385,20 +4682,20 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="21"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="23"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="22"/>
+      <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -5423,14 +4720,14 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="19"/>
-      <c r="K21" s="19" t="s">
+      <c r="I21" s="21"/>
+      <c r="K21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="19"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
@@ -5476,10 +4773,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="19"/>
+      <c r="F24" s="21"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -5536,10 +4833,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="19"/>
+      <c r="C27" s="21"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -5736,7 +5033,7 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="K35" s="22"/>
+      <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
@@ -5747,10 +5044,10 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="20" t="s">
+      <c r="H36" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="21"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
@@ -5766,10 +5063,10 @@
       <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="19" t="s">
+      <c r="K37" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="19"/>
+      <c r="L37" s="21"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
@@ -6021,7 +5318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6237,21 +5534,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -6452,24 +5734,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6486,4 +5766,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEEAE248-AADC-4AD7-8E2F-83EB68A3E958}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 3 - 14 al 18 de Oct  " sheetId="28" r:id="rId3"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
+    <sheet name="Semana 2 - 14 de Oct  " sheetId="29" r:id="rId3"/>
+    <sheet name="Semana 2 - 15 al 18 de Oct" sheetId="30" r:id="rId4"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -651,7 +652,217 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="143">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3089,124 +3300,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4105,141 +4316,141 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19CBA288-5685-457A-944C-50C7B2C8074B}">
-  <dimension ref="B2:L45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
+  <dimension ref="B2:G40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
@@ -4251,7 +4462,7 @@
     <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -4261,6 +4472,555 @@
         <v>1</v>
       </c>
       <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="C24" s="1"/>
+      <c r="E24" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="18"/>
+      <c r="C25" s="1"/>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
+      <c r="C26" s="1"/>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
+      <c r="D38"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
+      <c r="D39"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
+      <c r="D40"/>
+      <c r="F40" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="61" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17 B12">
+    <cfRule type="duplicateValues" dxfId="58" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29 B11">
+    <cfRule type="duplicateValues" dxfId="56" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B23:B26">
+    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="54" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B9">
+    <cfRule type="duplicateValues" dxfId="52" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="51" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="50" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="49" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="48" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="47" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="45" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="44" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="42" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="41" priority="4"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
+  <dimension ref="B2:L45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
       <c r="H2" s="21" t="s">
         <v>2</v>
       </c>
@@ -4270,7 +5030,7 @@
       </c>
       <c r="L2" s="21"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -4297,7 +5057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4323,7 +5083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -4334,7 +5094,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>12</v>
@@ -4349,7 +5109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -4375,7 +5135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -4386,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>99</v>
@@ -4401,7 +5161,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -4427,7 +5187,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -4438,7 +5198,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>100</v>
@@ -4453,7 +5213,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -4479,7 +5239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -4490,7 +5250,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>15</v>
@@ -4505,7 +5265,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -4531,7 +5291,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -4543,7 +5303,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>103</v>
@@ -4558,7 +5318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -4585,7 +5345,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -4596,7 +5356,7 @@
         <v>110</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>105</v>
@@ -4611,7 +5371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -4639,12 +5399,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>110</v>
@@ -4660,7 +5421,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -4681,7 +5443,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
@@ -4690,7 +5452,7 @@
         <v>33</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H19" s="19"/>
       <c r="I19" s="20"/>
@@ -4698,7 +5460,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -4712,7 +5474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -4720,6 +5482,7 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
+      <c r="F21" s="1"/>
       <c r="H21" s="21" t="s">
         <v>27</v>
       </c>
@@ -4729,7 +5492,7 @@
       </c>
       <c r="L21" s="21"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -4737,6 +5500,7 @@
         <v>32</v>
       </c>
       <c r="E22" s="18"/>
+      <c r="F22" s="1"/>
       <c r="H22" s="3" t="s">
         <v>6</v>
       </c>
@@ -4750,14 +5514,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="2"/>
       <c r="H23" s="11" t="s">
         <v>98</v>
       </c>
@@ -4768,11 +5531,12 @@
         <v>90</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
+      <c r="C24" s="1"/>
       <c r="E24" s="21" t="s">
         <v>89</v>
       </c>
@@ -4787,11 +5551,12 @@
         <v>16</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
+      <c r="C25" s="1"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
@@ -4808,16 +5573,17 @@
         <v>91</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
+      <c r="C26" s="1"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>7</v>
@@ -4829,10 +5595,10 @@
         <v>7</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="21" t="s">
         <v>36</v>
       </c>
@@ -4841,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>20</v>
@@ -4853,10 +5619,10 @@
         <v>20</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -4867,7 +5633,7 @@
         <v>41</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>101</v>
@@ -4879,10 +5645,10 @@
         <v>92</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -4893,7 +5659,7 @@
         <v>79</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>17</v>
@@ -4905,10 +5671,10 @@
         <v>17</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -4919,7 +5685,7 @@
         <v>114</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>23</v>
@@ -4931,10 +5697,10 @@
         <v>23</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -4945,7 +5711,7 @@
         <v>115</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>22</v>
@@ -4957,10 +5723,10 @@
         <v>22</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -4968,6 +5734,7 @@
         <v>14</v>
       </c>
       <c r="D32"/>
+      <c r="F32" s="1"/>
       <c r="H32" s="11" t="s">
         <v>105</v>
       </c>
@@ -4978,10 +5745,10 @@
         <v>93</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -4989,6 +5756,7 @@
         <v>14</v>
       </c>
       <c r="D33"/>
+      <c r="F33" s="1"/>
       <c r="H33" s="8" t="s">
         <v>77</v>
       </c>
@@ -5000,10 +5768,10 @@
         <v>77</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -5011,6 +5779,7 @@
         <v>8</v>
       </c>
       <c r="D34"/>
+      <c r="F34" s="1"/>
       <c r="H34" s="17" t="s">
         <v>110</v>
       </c>
@@ -5022,10 +5791,10 @@
         <v>110</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -5033,10 +5802,11 @@
         <v>8</v>
       </c>
       <c r="D35"/>
+      <c r="F35" s="1"/>
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -5044,12 +5814,13 @@
         <v>8</v>
       </c>
       <c r="D36"/>
+      <c r="F36" s="1"/>
       <c r="H36" s="22" t="s">
         <v>44</v>
       </c>
       <c r="I36" s="23"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -5057,6 +5828,7 @@
         <v>43</v>
       </c>
       <c r="D37"/>
+      <c r="F37" s="1"/>
       <c r="H37" s="3" t="s">
         <v>37</v>
       </c>
@@ -5068,8 +5840,10 @@
       </c>
       <c r="L37" s="21"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
       <c r="D38"/>
+      <c r="F38" s="1"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
       </c>
@@ -5083,8 +5857,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
       <c r="D39"/>
+      <c r="F39" s="1"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
       </c>
@@ -5098,8 +5874,10 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
       <c r="D40"/>
+      <c r="F40" s="1"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
       </c>
@@ -5113,7 +5891,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="1"/>
+      <c r="F41" s="1"/>
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -5127,7 +5907,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="1"/>
+      <c r="F42" s="1"/>
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -5141,7 +5923,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="1"/>
+      <c r="F43" s="1"/>
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -5155,7 +5939,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="1"/>
+      <c r="F44" s="1"/>
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -5169,7 +5955,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="1"/>
+      <c r="F45" s="1"/>
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -5179,6 +5967,7 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
@@ -5189,7 +5978,6 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="40" priority="35"/>
@@ -5318,7 +6106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5534,6 +6322,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -5734,22 +6537,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5766,21 +6571,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEEAE248-AADC-4AD7-8E2F-83EB68A3E958}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30DCBA9-82F6-49D6-B8FB-327247DCC15A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 2 - 14 de Oct  " sheetId="29" r:id="rId3"/>
-    <sheet name="Semana 2 - 15 al 18 de Oct" sheetId="30" r:id="rId4"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
+    <sheet name="Semana 2 - 12 al 13 Oct" sheetId="32" r:id="rId3"/>
+    <sheet name="Semana 2 - 14 de Oct  " sheetId="29" r:id="rId4"/>
+    <sheet name="Semana 2 - 15 al 18 de Oct" sheetId="30" r:id="rId5"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -652,7 +653,207 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="143">
+  <dxfs count="163">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3300,124 +3501,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="142" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="141" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="140" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="139" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="137" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="136" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="135" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="134" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="133" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="132" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="131" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="130" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="129" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="128" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="127" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="126" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="125" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="124" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="123" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="122" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="121" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="120" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="119" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="118" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="117" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="116" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="115" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="114" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="113" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="112" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="111" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="110" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="109" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="108" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="107" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="106" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="105" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="104" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="103" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4316,133 +4517,635 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="102" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="101" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="100" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="99" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="98" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="97" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="96" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="95" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="93" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="92" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="91" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="90" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="89" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="88" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="87" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="86" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="85" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="84" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="83" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="82" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="81" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="79" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="78" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="77" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="75" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="74" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="73" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="72" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="71" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="70" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="69" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="68" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="67" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="66" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="65" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="64" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86259B90-4A78-45A3-AC3D-5D90B4EC10BE}">
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="18"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="18"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D41"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="OJkidEuN0Ozb3Zbys7HXsM0LmiJsyXlHUTxKQ3IQAwjdoRjrbgFYj/oQ/q47z6jHIVLSbhDHYUyyc06ZDczV5A==" saltValue="ycZhDaBtwKOzMRLur/NcbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E24:F24"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B12">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25 B11">
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B21:B22">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B10">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B9">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
   <dimension ref="B2:G40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4462,7 +5165,7 @@
     <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -4473,7 +5176,7 @@
       </c>
       <c r="F2" s="21"/>
     </row>
-    <row r="3" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -4488,7 +5191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4502,7 +5205,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -4516,7 +5219,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -4530,7 +5233,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -4544,7 +5247,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -4558,7 +5261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -4572,7 +5275,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -4586,7 +5289,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -4600,7 +5303,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -4614,7 +5317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -4629,7 +5332,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -4644,7 +5347,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -4658,7 +5361,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -4673,8 +5376,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="1"/>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -4682,8 +5384,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="1"/>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -4691,7 +5392,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
@@ -4703,7 +5404,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="2:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -4717,7 +5418,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -4725,9 +5426,8 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -4735,27 +5435,25 @@
         <v>32</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
-      <c r="C24" s="1"/>
       <c r="E24" s="21" t="s">
         <v>89</v>
       </c>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="C25" s="1"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
@@ -4763,9 +5461,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
-      <c r="C26" s="1"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
       </c>
@@ -4773,7 +5470,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="21" t="s">
         <v>36</v>
       </c>
@@ -4785,7 +5482,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -4799,7 +5496,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -4813,7 +5510,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -4827,7 +5524,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -4841,7 +5538,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -4849,9 +5546,8 @@
         <v>14</v>
       </c>
       <c r="D32"/>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -4859,9 +5555,8 @@
         <v>14</v>
       </c>
       <c r="D33"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -4869,9 +5564,8 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -4879,9 +5573,8 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -4889,9 +5582,8 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -4899,22 +5591,15 @@
         <v>43</v>
       </c>
       <c r="D37"/>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="1"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="1"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="1"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D40"/>
-      <c r="F40" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4925,73 +5610,73 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="61" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="58" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="56" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="55" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="54" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="52" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="51" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="50" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="49" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="48" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="47" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="45" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="44" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="42" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="41" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
   <dimension ref="B2:L45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5011,7 +5696,7 @@
     <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -5030,7 +5715,7 @@
       </c>
       <c r="L2" s="21"/>
     </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -5057,7 +5742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5083,7 +5768,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5109,7 +5794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -5135,7 +5820,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -5161,7 +5846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -5187,7 +5872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5213,7 +5898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5239,7 +5924,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -5265,7 +5950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5291,7 +5976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -5318,7 +6003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -5345,7 +6030,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -5371,7 +6056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -5399,8 +6084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="1"/>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -5421,8 +6105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="1"/>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -5443,7 +6126,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
@@ -5460,7 +6143,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -5474,7 +6157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -5482,7 +6165,6 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="F21" s="1"/>
       <c r="H21" s="21" t="s">
         <v>27</v>
       </c>
@@ -5492,7 +6174,7 @@
       </c>
       <c r="L21" s="21"/>
     </row>
-    <row r="22" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -5500,7 +6182,6 @@
         <v>32</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="F22" s="1"/>
       <c r="H22" s="3" t="s">
         <v>6</v>
       </c>
@@ -5514,13 +6195,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="F23" s="2"/>
       <c r="H23" s="11" t="s">
         <v>98</v>
       </c>
@@ -5534,9 +6216,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
-      <c r="C24" s="1"/>
       <c r="E24" s="21" t="s">
         <v>89</v>
       </c>
@@ -5554,9 +6235,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="C25" s="1"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
@@ -5576,9 +6256,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
-      <c r="C26" s="1"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
       </c>
@@ -5598,7 +6277,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="21" t="s">
         <v>36</v>
       </c>
@@ -5622,7 +6301,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -5648,7 +6327,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -5674,7 +6353,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -5700,7 +6379,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -5726,7 +6405,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -5734,7 +6413,6 @@
         <v>14</v>
       </c>
       <c r="D32"/>
-      <c r="F32" s="1"/>
       <c r="H32" s="11" t="s">
         <v>105</v>
       </c>
@@ -5748,7 +6426,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -5756,7 +6434,6 @@
         <v>14</v>
       </c>
       <c r="D33"/>
-      <c r="F33" s="1"/>
       <c r="H33" s="8" t="s">
         <v>77</v>
       </c>
@@ -5771,7 +6448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -5779,7 +6456,6 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="F34" s="1"/>
       <c r="H34" s="17" t="s">
         <v>110</v>
       </c>
@@ -5794,7 +6470,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -5802,11 +6478,10 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="F35" s="1"/>
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -5814,13 +6489,12 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="F36" s="1"/>
       <c r="H36" s="22" t="s">
         <v>44</v>
       </c>
       <c r="I36" s="23"/>
     </row>
-    <row r="37" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -5828,7 +6502,6 @@
         <v>43</v>
       </c>
       <c r="D37"/>
-      <c r="F37" s="1"/>
       <c r="H37" s="3" t="s">
         <v>37</v>
       </c>
@@ -5840,10 +6513,8 @@
       </c>
       <c r="L37" s="21"/>
     </row>
-    <row r="38" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="1"/>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
-      <c r="F38" s="1"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
       </c>
@@ -5857,10 +6528,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="1"/>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
-      <c r="F39" s="1"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
       </c>
@@ -5874,10 +6543,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="1"/>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
-      <c r="F40" s="1"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
       </c>
@@ -5891,9 +6558,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="1"/>
-      <c r="F41" s="1"/>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -5907,9 +6572,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="1"/>
-      <c r="F42" s="1"/>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -5923,9 +6586,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="1"/>
-      <c r="F43" s="1"/>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -5939,9 +6600,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="1"/>
-      <c r="F44" s="1"/>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -5955,9 +6614,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="2:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="1"/>
-      <c r="F45" s="1"/>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -5967,146 +6624,146 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="H21:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6331,12 +6988,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -6537,6 +7188,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
@@ -6546,15 +7203,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6571,4 +7219,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,20 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{6D305847-F0F7-4584-B544-A43B41FEE209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30DCBA9-82F6-49D6-B8FB-327247DCC15A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CB0DF-D4E7-4BFB-8FB8-7AE0678772A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 2 - 12 al 13 Oct" sheetId="32" r:id="rId3"/>
-    <sheet name="Semana 2 - 14 de Oct  " sheetId="29" r:id="rId4"/>
-    <sheet name="Semana 2 - 15 al 18 de Oct" sheetId="30" r:id="rId5"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId6"/>
+    <sheet name="Semana 3 - 14 al 18 de Oct 1 " sheetId="29" r:id="rId3"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -438,7 +436,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -488,6 +486,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -582,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -637,9 +646,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -649,421 +655,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="163">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="122">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2633,23 +2241,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="H3" s="21" t="s">
+      <c r="F3" s="20"/>
+      <c r="H3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="K3" s="21" t="s">
+      <c r="I3" s="20"/>
+      <c r="K3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="21"/>
+      <c r="L3" s="20"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -3036,10 +2644,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="20"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
@@ -3060,14 +2668,14 @@
       <c r="F20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="K20" s="21" t="s">
+      <c r="I20" s="20"/>
+      <c r="K20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="21"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
@@ -3112,10 +2720,10 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="21"/>
+      <c r="F23" s="20"/>
       <c r="H23" s="11" t="s">
         <v>16</v>
       </c>
@@ -3130,10 +2738,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="21"/>
+      <c r="C24" s="20"/>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
@@ -3377,14 +2985,14 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="23"/>
-      <c r="K35" s="21" t="s">
+      <c r="I35" s="22"/>
+      <c r="K35" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="21"/>
+      <c r="L35" s="20"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
@@ -3501,124 +3109,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="162" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="161" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="160" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="159" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="158" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="157" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="156" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="155" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="154" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="153" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="152" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="151" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="149" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="148" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="147" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="146" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="145" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="144" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="143" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="142" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="141" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="140" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="139" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="138" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="137" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="136" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="135" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="134" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="133" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="132" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="131" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="130" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="129" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="128" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="127" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="126" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="125" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="124" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="123" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3645,23 +3253,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20"/>
+      <c r="H2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20"/>
+      <c r="K2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
@@ -4048,10 +3656,10 @@
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="20"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -4072,14 +3680,14 @@
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="K19" s="21" t="s">
+      <c r="I19" s="20"/>
+      <c r="K19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="21"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -4188,10 +3796,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="21"/>
+      <c r="F25" s="20"/>
       <c r="H25" s="11" t="s">
         <v>20</v>
       </c>
@@ -4206,10 +3814,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="21"/>
+      <c r="C26" s="20"/>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
@@ -4393,14 +4001,14 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="23"/>
-      <c r="K34" s="21" t="s">
+      <c r="I34" s="22"/>
+      <c r="K34" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="21"/>
+      <c r="L34" s="20"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
@@ -4517,1169 +4125,136 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="122" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="121" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="120" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="119" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="118" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="117" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="116" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="115" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="114" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="113" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="105" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="103" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="93" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="92" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="91" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="90" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="89" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="88" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="87" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="86" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="85" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="84" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="83" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="82" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86259B90-4A78-45A3-AC3D-5D90B4EC10BE}">
-  <dimension ref="B2:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="E16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="21"/>
-      <c r="E18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="18"/>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="18"/>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D41"/>
-    </row>
-  </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OJkidEuN0Ozb3Zbys7HXsM0LmiJsyXlHUTxKQ3IQAwjdoRjrbgFYj/oQ/q47z6jHIVLSbhDHYUyyc06ZDczV5A==" saltValue="ycZhDaBtwKOzMRLur/NcbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="5">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E24:F24"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
-  <dimension ref="B2:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="E19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="18"/>
-      <c r="E24" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="18"/>
-      <c r="E25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="18"/>
-      <c r="E26" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="21"/>
-      <c r="E27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D39"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D40"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B19:C19"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="81" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="78" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="77" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="76" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="75" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="72" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="70" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="69" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="67" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="65" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="62" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="61" priority="4"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227B4AC7-07F2-471A-87D3-1EC4FE829A48}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
@@ -5697,48 +4272,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20"/>
+      <c r="H2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20"/>
+      <c r="K2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5764,7 +4339,7 @@
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5784,7 +4359,7 @@
       <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -5816,7 +4391,7 @@
       <c r="K6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5836,7 +4411,7 @@
       <c r="H7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="8" t="s">
@@ -5868,7 +4443,7 @@
       <c r="K8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5888,7 +4463,7 @@
       <c r="H9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -5920,7 +4495,7 @@
       <c r="K10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5940,7 +4515,7 @@
       <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K11" s="6" t="s">
@@ -5972,7 +4547,7 @@
       <c r="K12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5993,7 +4568,7 @@
       <c r="H13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K13" s="6" t="s">
@@ -6026,7 +4601,7 @@
       <c r="K14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6046,7 +4621,7 @@
       <c r="H15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="24" t="s">
         <v>43</v>
       </c>
       <c r="K15" s="9" t="s">
@@ -6080,7 +4655,7 @@
       <c r="K16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6094,7 +4669,7 @@
       <c r="H17" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="24" t="s">
         <v>43</v>
       </c>
       <c r="J17" s="1"/>
@@ -6122,15 +4697,15 @@
       <c r="K18" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="24" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="20"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -6138,16 +4713,16 @@
         <v>109</v>
       </c>
       <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
+      <c r="I19" s="25"/>
       <c r="J19" s="1"/>
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="8" t="s">
@@ -6165,14 +4740,14 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="K21" s="21" t="s">
+      <c r="I21" s="20"/>
+      <c r="K21" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="21"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
@@ -6182,16 +4757,16 @@
         <v>32</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="L22" s="26" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6218,10 +4793,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="21"/>
+      <c r="F24" s="20"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -6237,10 +4812,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="23" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
@@ -6278,10 +4853,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="20"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -6302,10 +4877,10 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="23" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="6" t="s">
@@ -6489,10 +5064,10 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="23"/>
+      <c r="I36" s="22"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
@@ -6502,16 +5077,16 @@
         <v>43</v>
       </c>
       <c r="D37"/>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="21"/>
+      <c r="L37" s="20"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
@@ -6521,10 +5096,10 @@
       <c r="I38" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="L38" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6624,146 +5199,146 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K37:L37"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H21:I21"/>
     <mergeCell ref="K21:L21"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="H21:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="60" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="59" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="58" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="56" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="54" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="53" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="52" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="51" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="50" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="49" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="48" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="46" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="44" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="39" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="38" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="37" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="36" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="28" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="27" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6988,6 +5563,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -7188,12 +5769,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
@@ -7203,6 +5778,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7219,13 +5803,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,18 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CB0DF-D4E7-4BFB-8FB8-7AE0678772A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8932C86-8D14-408D-91EB-7486DE78F6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="5" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
     <sheet name="Semana 2 - 05 al 11 de Oct Sep" sheetId="25" r:id="rId2"/>
-    <sheet name="Semana 3 - 14 al 18 de Oct 1 " sheetId="29" r:id="rId3"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
+    <sheet name="Semana 3 - 12 al 13 Oct" sheetId="32" r:id="rId3"/>
+    <sheet name="Semana 3 - 14 de Oct  " sheetId="29" r:id="rId4"/>
+    <sheet name="Semana 3 - 15 al 18 de Oct" sheetId="30" r:id="rId5"/>
+    <sheet name="Semana 4 - 19 al 25 de Oct" sheetId="33" r:id="rId6"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="118">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -436,7 +439,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,17 +489,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -591,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,6 +638,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -655,23 +650,831 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="204">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2241,23 +3044,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="H3" s="20" t="s">
+      <c r="F3" s="21"/>
+      <c r="H3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="K3" s="20" t="s">
+      <c r="I3" s="21"/>
+      <c r="K3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="20"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -2644,10 +3447,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
@@ -2668,14 +3471,14 @@
       <c r="F20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="20"/>
-      <c r="K20" s="20" t="s">
+      <c r="I20" s="21"/>
+      <c r="K20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="20"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
@@ -2720,10 +3523,10 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="20"/>
+      <c r="F23" s="21"/>
       <c r="H23" s="11" t="s">
         <v>16</v>
       </c>
@@ -2738,10 +3541,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="20"/>
+      <c r="C24" s="21"/>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
@@ -2985,14 +3788,14 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="22"/>
-      <c r="K35" s="20" t="s">
+      <c r="I35" s="23"/>
+      <c r="K35" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="20"/>
+      <c r="L35" s="21"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
@@ -3109,124 +3912,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="121" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="120" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="119" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="118" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="117" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="116" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="115" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="114" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="113" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="108" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="105" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="104" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="103" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="102" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="101" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="100" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="99" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="98" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="97" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="96" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="93" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="92" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="91" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="88" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="87" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="86" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="85" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="84" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="83" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="82" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3253,23 +4056,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="H2" s="20" t="s">
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="20"/>
-      <c r="K2" s="20" t="s">
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="20"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
@@ -3656,10 +4459,10 @@
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="20"/>
+      <c r="C18" s="21"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -3680,14 +4483,14 @@
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="K19" s="20" t="s">
+      <c r="I19" s="21"/>
+      <c r="K19" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="20"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -3796,10 +4599,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="20"/>
+      <c r="F25" s="21"/>
       <c r="H25" s="11" t="s">
         <v>20</v>
       </c>
@@ -3814,10 +4617,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="20"/>
+      <c r="C26" s="21"/>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
@@ -4001,14 +4804,14 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="22"/>
-      <c r="K34" s="20" t="s">
+      <c r="I34" s="23"/>
+      <c r="K34" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="20"/>
+      <c r="L34" s="21"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
@@ -4125,136 +4928,1169 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="77" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="60" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="56" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="53" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="52" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="48" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="46" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="44" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="43" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227B4AC7-07F2-471A-87D3-1EC4FE829A48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86259B90-4A78-45A3-AC3D-5D90B4EC10BE}">
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="18"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="18"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D41"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="OJkidEuN0Ozb3Zbys7HXsM0LmiJsyXlHUTxKQ3IQAwjdoRjrbgFYj/oQ/q47z6jHIVLSbhDHYUyyc06ZDczV5A==" saltValue="ycZhDaBtwKOzMRLur/NcbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E24:F24"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="122" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="121" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="120" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B12">
+    <cfRule type="duplicateValues" dxfId="119" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25 B11">
+    <cfRule type="duplicateValues" dxfId="118" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B21:B22">
+    <cfRule type="duplicateValues" dxfId="117" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B10">
+    <cfRule type="duplicateValues" dxfId="116" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B9">
+    <cfRule type="duplicateValues" dxfId="115" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="114" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="113" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="112" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="111" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="110" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="109" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="108" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="107" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="106" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="105" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="104" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="103" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
+  <dimension ref="B2:G40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="E24" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="18"/>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="102" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="101" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="100" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17 B12">
+    <cfRule type="duplicateValues" dxfId="99" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="98" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29 B11">
+    <cfRule type="duplicateValues" dxfId="97" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B23:B26">
+    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="95" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B9">
+    <cfRule type="duplicateValues" dxfId="93" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="92" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="91" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="90" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="88" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="87" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="85" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="84" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="83" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
@@ -4272,48 +6108,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="H2" s="20" t="s">
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="20"/>
-      <c r="K2" s="20" t="s">
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="20"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4339,7 +6175,7 @@
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4359,7 +6195,7 @@
       <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -4391,7 +6227,7 @@
       <c r="K6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="24" t="s">
+      <c r="L6" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4411,7 +6247,7 @@
       <c r="H7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="8" t="s">
@@ -4443,7 +6279,7 @@
       <c r="K8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4463,7 +6299,7 @@
       <c r="H9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -4495,7 +6331,7 @@
       <c r="K10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4515,7 +6351,7 @@
       <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K11" s="6" t="s">
@@ -4547,7 +6383,7 @@
       <c r="K12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4568,7 +6404,7 @@
       <c r="H13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K13" s="6" t="s">
@@ -4601,7 +6437,7 @@
       <c r="K14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="24" t="s">
+      <c r="L14" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4621,7 +6457,7 @@
       <c r="H15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="I15" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K15" s="9" t="s">
@@ -4655,7 +6491,7 @@
       <c r="K16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="24" t="s">
+      <c r="L16" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4669,7 +6505,7 @@
       <c r="H17" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="I17" s="7" t="s">
         <v>43</v>
       </c>
       <c r="J17" s="1"/>
@@ -4697,15 +6533,15 @@
       <c r="K18" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="L18" s="24" t="s">
+      <c r="L18" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -4713,16 +6549,16 @@
         <v>109</v>
       </c>
       <c r="H19" s="19"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="20"/>
       <c r="J19" s="1"/>
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="23" t="s">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="8" t="s">
@@ -4740,14 +6576,14 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="20"/>
-      <c r="K21" s="20" t="s">
+      <c r="I21" s="21"/>
+      <c r="K21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="20"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
@@ -4757,16 +6593,16 @@
         <v>32</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="26" t="s">
+      <c r="L22" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4793,10 +6629,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="20"/>
+      <c r="F24" s="21"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -4812,10 +6648,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="11" t="s">
@@ -4853,10 +6689,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="20"/>
+      <c r="C27" s="21"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -4877,10 +6713,10 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="6" t="s">
@@ -5064,10 +6900,10 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="22"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
@@ -5077,16 +6913,16 @@
         <v>43</v>
       </c>
       <c r="D37"/>
-      <c r="H37" s="23" t="s">
+      <c r="H37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="20" t="s">
+      <c r="K37" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="20"/>
+      <c r="L37" s="21"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
@@ -5096,10 +6932,10 @@
       <c r="I38" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="K38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L38" s="23" t="s">
+      <c r="L38" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5195,6 +7031,1092 @@
       </c>
       <c r="L45" s="5" t="s">
         <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17 B12">
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="77" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29 B11">
+    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B23:B26">
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B9">
+    <cfRule type="duplicateValues" dxfId="72" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E22">
+    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="60" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="59" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="57" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:H29">
+    <cfRule type="duplicateValues" dxfId="54" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H41">
+    <cfRule type="duplicateValues" dxfId="52" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H42">
+    <cfRule type="duplicateValues" dxfId="51" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="50" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="49" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="46" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27">
+    <cfRule type="duplicateValues" dxfId="45" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:K29">
+    <cfRule type="duplicateValues" dxfId="44" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33">
+    <cfRule type="duplicateValues" dxfId="43" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K42">
+    <cfRule type="duplicateValues" dxfId="42" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
+    <cfRule type="duplicateValues" dxfId="41" priority="19"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A327CFEE-00BE-49D5-8C69-5CD256340320}">
+  <dimension ref="B2:L45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="21"/>
+      <c r="K21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="21"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="H22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="H23" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="E24" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="H24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="18"/>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="H32" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+      <c r="H33" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+      <c r="H36" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="23"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+      <c r="H37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="21"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+      <c r="H38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+      <c r="H39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+      <c r="H40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K45" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5268,7 +8190,7 @@
   <conditionalFormatting sqref="E19">
     <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E20:E22">
+  <conditionalFormatting sqref="E20 E22">
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
@@ -5338,7 +8260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5554,21 +8476,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -5769,24 +8682,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5803,4 +8725,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D8932C86-8D14-408D-91EB-7486DE78F6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="5" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
@@ -7035,17 +7035,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="81" priority="35"/>
@@ -8476,9 +8476,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8683,27 +8686,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8728,9 +8719,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8932C86-8D14-408D-91EB-7486DE78F6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEEEDB2-034E-41EB-8D8D-4B6550D0DA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="816" firstSheet="3" activeTab="6" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="Semana 3 - 14 de Oct  " sheetId="29" r:id="rId4"/>
     <sheet name="Semana 3 - 15 al 18 de Oct" sheetId="30" r:id="rId5"/>
     <sheet name="Semana 4 - 19 al 25 de Oct" sheetId="33" r:id="rId6"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId7"/>
+    <sheet name="Semana 5 - 26 de Oct" sheetId="34" r:id="rId7"/>
+    <sheet name="Semana 5 - 27 Oct al 1 de Nov" sheetId="35" r:id="rId8"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="119">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -434,12 +436,15 @@
   <si>
     <t xml:space="preserve">Apoyo en tareas operativas según asignación </t>
   </si>
+  <si>
+    <t>Seguimiento Abuso de Bonos (Correo) - Cada Hora</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +494,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -583,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -650,11 +666,1313 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="204">
+  <dxfs count="333">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3912,124 +5230,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="203" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="202" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="201" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="200" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="199" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="198" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="197" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="196" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="195" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="194" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="193" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="192" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="191" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="190" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="189" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="188" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="187" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="186" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="185" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="184" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="183" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="182" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="181" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="180" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="179" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="178" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="177" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="176" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="175" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="174" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="172" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="171" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="170" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="169" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="168" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="167" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="166" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="165" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="164" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4928,127 +6246,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="163" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="162" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="161" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="160" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="159" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="158" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="157" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="156" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="155" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="154" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="153" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="152" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="151" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="150" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="149" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="148" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="147" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="146" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="145" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="144" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="143" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="142" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="141" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="140" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="139" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="138" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="137" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="136" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="135" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="134" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="133" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="132" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="131" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="130" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="129" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="128" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="127" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="126" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="125" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="124" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="123" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5493,64 +6811,64 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="122" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="121" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="120" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="119" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="118" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="117" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="116" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="115" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="114" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="113" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="112" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="111" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="110" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="109" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="108" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="107" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="106" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="105" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="104" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="103" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5564,7 +6882,7 @@
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
@@ -6021,67 +7339,67 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="102" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="101" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="100" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="99" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="98" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="97" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="96" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="95" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="93" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="92" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="91" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="90" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="89" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="88" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="87" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="85" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="84" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="83" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6095,7 +7413,7 @@
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
@@ -7048,127 +8366,127 @@
     <mergeCell ref="H21:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="81" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="80" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="77" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="76" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="72" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="71" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="68" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="67" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="66" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="65" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="64" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="63" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="62" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="61" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="60" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="59" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="57" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="56" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="54" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="52" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="51" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="50" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="49" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="46" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="45" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="44" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="43" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="42" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="41" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7182,7 +8500,7 @@
     <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
@@ -8134,139 +9452,1758 @@
     <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="39" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22">
-    <cfRule type="duplicateValues" dxfId="21" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9FC74A-71CC-442B-A4E0-26218C5C155E}">
+  <dimension ref="B2:G40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="18"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="E19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E23:F23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="128" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="127" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="126" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17 B12">
+    <cfRule type="duplicateValues" dxfId="125" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21 B11">
+    <cfRule type="duplicateValues" dxfId="124" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23 B18">
+    <cfRule type="duplicateValues" dxfId="123" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24 B10">
+    <cfRule type="duplicateValues" dxfId="122" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="121" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B9">
+    <cfRule type="duplicateValues" dxfId="120" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="119" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="118" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="117" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="116" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="115" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="114" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="113" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="112" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="111" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:E21">
+    <cfRule type="duplicateValues" dxfId="110" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28">
+    <cfRule type="duplicateValues" dxfId="109" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949C4FB1-0786-48FB-AC2F-6783FDA539CA}">
+  <dimension ref="B2:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="H2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="K2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C15" s="2"/>
+      <c r="E15" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C16" s="2"/>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="E17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="H19" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="26"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="18"/>
+      <c r="H22" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="21"/>
+      <c r="K22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="21"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C27" s="2"/>
+      <c r="E27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="18"/>
+      <c r="E28" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="H29" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="H32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+      <c r="H33" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35"/>
+      <c r="H35" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+      <c r="H36" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38"/>
+      <c r="H38" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="22"/>
+      <c r="K38" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L38" s="21"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39"/>
+      <c r="H39" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K39" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40"/>
+      <c r="H40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H46" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="42" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="41" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="38" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B11">
+    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33 B28">
+    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="30" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26">
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="duplicateValues" dxfId="20" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29:H30">
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H43">
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H44">
+    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28">
+    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K29:K30">
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34">
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -8476,15 +11413,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -8685,21 +11613,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8718,7 +11647,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -8733,4 +11662,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEEEDB2-034E-41EB-8D8D-4B6550D0DA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39C5F4F-6D58-4D93-9CB1-A0CAC61E4002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="816" firstSheet="3" activeTab="6" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="2" activeTab="6" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Semana 3 - 14 de Oct  " sheetId="29" r:id="rId4"/>
     <sheet name="Semana 3 - 15 al 18 de Oct" sheetId="30" r:id="rId5"/>
     <sheet name="Semana 4 - 19 al 25 de Oct" sheetId="33" r:id="rId6"/>
-    <sheet name="Semana 5 - 26 de Oct" sheetId="34" r:id="rId7"/>
+    <sheet name="Semana 5 - 26 Oct al 26 Oct" sheetId="34" r:id="rId7"/>
     <sheet name="Semana 5 - 27 Oct al 1 de Nov" sheetId="35" r:id="rId8"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId9"/>
   </sheets>
@@ -657,15 +657,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -678,671 +669,20 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="333">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="267">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4344,43 +3684,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AC30FF-4C9E-4211-B41D-FEC83E8B88B1}">
   <dimension ref="B3:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="21" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="H3" s="21" t="s">
+      <c r="F3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="K3" s="21" t="s">
+      <c r="I3" s="25"/>
+      <c r="K3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="21"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -4407,7 +3747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -4433,7 +3773,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
@@ -4459,7 +3799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -4485,7 +3825,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
@@ -4511,7 +3851,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
@@ -4537,7 +3877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
@@ -4563,7 +3903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
@@ -4589,7 +3929,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>29</v>
       </c>
@@ -4615,7 +3955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
@@ -4641,7 +3981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>102</v>
       </c>
@@ -4668,7 +4008,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>104</v>
       </c>
@@ -4695,7 +4035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>95</v>
       </c>
@@ -4721,7 +4061,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
@@ -4743,7 +4083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E18" s="6" t="s">
         <v>25</v>
       </c>
@@ -4764,11 +4104,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
@@ -4776,7 +4116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -4789,16 +4129,16 @@
       <c r="F20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="K20" s="21" t="s">
+      <c r="I20" s="25"/>
+      <c r="K20" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="21"/>
-    </row>
-    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L20" s="25"/>
+    </row>
+    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -4824,7 +4164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="18"/>
       <c r="F22" s="2"/>
       <c r="H22" s="11" t="s">
@@ -4840,11 +4180,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E23" s="21" t="s">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E23" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="21"/>
+      <c r="F23" s="25"/>
       <c r="H23" s="11" t="s">
         <v>16</v>
       </c>
@@ -4858,11 +4198,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="21" t="s">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="21"/>
+      <c r="C24" s="25"/>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
@@ -4882,7 +4222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
@@ -4908,7 +4248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
@@ -4934,7 +4274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="16" t="s">
         <v>34</v>
       </c>
@@ -4960,7 +4300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="8" t="s">
         <v>77</v>
       </c>
@@ -4986,7 +4326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>22</v>
       </c>
@@ -5006,7 +4346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
@@ -5026,7 +4366,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>40</v>
       </c>
@@ -5046,7 +4386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
@@ -5067,7 +4407,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="12" t="s">
         <v>78</v>
       </c>
@@ -5089,7 +4429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -5098,7 +4438,7 @@
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -5106,16 +4446,16 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="23"/>
-      <c r="K35" s="21" t="s">
+      <c r="I35" s="27"/>
+      <c r="K35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="21"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L35" s="25"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
         <v>42</v>
       </c>
@@ -5136,7 +4476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>12</v>
@@ -5151,7 +4491,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>16</v>
@@ -5166,7 +4506,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>41</v>
@@ -5181,7 +4521,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>22</v>
@@ -5196,7 +4536,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D41"/>
       <c r="H41" s="6" t="s">
         <v>21</v>
@@ -5211,7 +4551,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D42"/>
     </row>
   </sheetData>
@@ -5230,124 +4570,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="332" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="331" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="330" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="329" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="328" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="327" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="326" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="325" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="324" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="323" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="322" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="321" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="320" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="319" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="318" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="317" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="316" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="315" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="314" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="313" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="312" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="311" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="310" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="309" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="308" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="307" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="306" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="305" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="304" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="303" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="302" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="301" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="300" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="299" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="298" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="297" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="296" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="295" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="294" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="293" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5356,43 +4696,43 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D300C407-A034-411B-B7F2-D7830F6D8BD1}">
   <dimension ref="B2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="4" max="4" width="11.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="25"/>
+      <c r="K2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -5419,7 +4759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5445,7 +4785,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5471,7 +4811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -5497,7 +4837,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -5523,7 +4863,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -5549,7 +4889,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5575,7 +4915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5601,7 +4941,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -5627,7 +4967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5653,7 +4993,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>94</v>
       </c>
@@ -5680,7 +5020,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
@@ -5707,7 +5047,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -5733,7 +5073,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -5755,7 +5095,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -5776,11 +5116,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="25"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -5788,7 +5128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -5801,16 +5141,16 @@
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="K19" s="21" t="s">
+      <c r="I19" s="25"/>
+      <c r="K19" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="21"/>
-    </row>
-    <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L19" s="25"/>
+    </row>
+    <row r="20" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -5836,7 +5176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>111</v>
       </c>
@@ -5862,7 +5202,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>112</v>
       </c>
@@ -5883,7 +5223,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="18"/>
       <c r="E23" s="18"/>
       <c r="H23" s="11" t="s">
@@ -5899,7 +5239,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
       <c r="F24" s="2"/>
       <c r="H24" s="11" t="s">
@@ -5915,12 +5255,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="21"/>
+      <c r="F25" s="25"/>
       <c r="H25" s="11" t="s">
         <v>20</v>
       </c>
@@ -5934,11 +5274,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="21"/>
+      <c r="C26" s="25"/>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
@@ -5958,7 +5298,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>4</v>
       </c>
@@ -5984,7 +5324,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="8" t="s">
         <v>26</v>
       </c>
@@ -6010,7 +5350,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="16" t="s">
         <v>34</v>
       </c>
@@ -6036,7 +5376,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
         <v>77</v>
       </c>
@@ -6062,7 +5402,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
@@ -6083,7 +5423,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
@@ -6105,7 +5445,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>40</v>
       </c>
@@ -6114,7 +5454,7 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -6122,16 +5462,16 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="23"/>
-      <c r="K34" s="21" t="s">
+      <c r="I34" s="27"/>
+      <c r="K34" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="21"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L34" s="25"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -6152,7 +5492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -6167,7 +5507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -6182,7 +5522,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>41</v>
@@ -6197,7 +5537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -6212,7 +5552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>21</v>
@@ -6227,7 +5567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D41"/>
     </row>
   </sheetData>
@@ -6246,127 +5586,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="292" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="291" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="290" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="289" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="288" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="287" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="286" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="285" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="284" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="283" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="282" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="281" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="280" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="279" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="278" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="277" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="276" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="275" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="274" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="273" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="272" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="271" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="270" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="269" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="268" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="267" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="266" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="265" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="264" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="263" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="262" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="261" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="260" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="259" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="258" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="257" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="256" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="255" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="254" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="253" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="252" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6375,30 +5715,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86259B90-4A78-45A3-AC3D-5D90B4EC10BE}">
   <dimension ref="B2:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="86.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="2"/>
+    <col min="4" max="4" width="6.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6413,7 +5753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -6427,7 +5767,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -6441,7 +5781,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -6455,7 +5795,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -6469,7 +5809,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -6483,7 +5823,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -6497,7 +5837,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -6511,7 +5851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -6525,7 +5865,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -6539,7 +5879,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -6554,7 +5894,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -6569,7 +5909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -6583,7 +5923,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -6592,7 +5932,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -6600,11 +5940,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="21" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="25"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -6612,7 +5952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6626,7 +5966,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -6640,34 +5980,34 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="18"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="21" t="s">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="21"/>
+      <c r="C23" s="25"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="25"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>26</v>
       </c>
@@ -6681,7 +6021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="16" t="s">
         <v>34</v>
       </c>
@@ -6695,7 +6035,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="s">
         <v>77</v>
       </c>
@@ -6709,7 +6049,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
@@ -6723,7 +6063,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>23</v>
       </c>
@@ -6737,7 +6077,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>40</v>
       </c>
@@ -6751,7 +6091,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>39</v>
       </c>
@@ -6759,7 +6099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
         <v>78</v>
       </c>
@@ -6768,7 +6108,7 @@
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
@@ -6777,28 +6117,28 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D35"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D36"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D37"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D38"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D39"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D40"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D41"/>
     </row>
   </sheetData>
@@ -6811,64 +6151,64 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="251" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="250" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="249" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="248" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="247" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="246" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="245" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="244" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="243" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="242" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="241" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="240" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="239" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="238" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="237" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="236" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="235" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="234" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="233" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="232" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6877,35 +6217,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
   <dimension ref="B2:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="13" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6920,7 +6260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -6934,7 +6274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -6948,7 +6288,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -6962,7 +6302,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -6976,7 +6316,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -6990,7 +6330,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -7004,7 +6344,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -7018,7 +6358,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -7032,7 +6372,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -7046,7 +6386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -7061,7 +6401,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -7076,7 +6416,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -7090,7 +6430,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -7105,7 +6445,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -7113,7 +6453,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -7121,11 +6461,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -7133,7 +6473,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -7147,7 +6487,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -7156,7 +6496,7 @@
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -7165,7 +6505,7 @@
       </c>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -7174,14 +6514,14 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="21"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="25"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -7190,7 +6530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -7199,11 +6539,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="25"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -7211,7 +6551,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -7225,7 +6565,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -7239,7 +6579,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -7253,7 +6593,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -7267,7 +6607,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -7276,7 +6616,7 @@
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -7285,7 +6625,7 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -7294,7 +6634,7 @@
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -7303,7 +6643,7 @@
       </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -7312,7 +6652,7 @@
       </c>
       <c r="D36"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -7321,13 +6661,13 @@
       </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D38"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D39"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D40"/>
     </row>
   </sheetData>
@@ -7339,67 +6679,67 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="231" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="230" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="229" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="228" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="227" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="226" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="225" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="224" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="223" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="222" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="221" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="220" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="219" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="218" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="217" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="216" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="215" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="214" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="213" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="212" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="211" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7408,43 +6748,43 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="13" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="25"/>
+      <c r="K2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -7471,7 +6811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -7497,7 +6837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -7523,7 +6863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -7549,7 +6889,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -7575,7 +6915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -7601,7 +6941,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -7627,7 +6967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -7653,7 +6993,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -7679,7 +7019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -7705,7 +7045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -7732,7 +7072,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -7759,7 +7099,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -7785,7 +7125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -7813,7 +7153,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -7834,7 +7174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -7855,11 +7195,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -7872,7 +7212,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -7886,7 +7226,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -7894,16 +7234,16 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="K21" s="21" t="s">
+      <c r="I21" s="25"/>
+      <c r="K21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="21"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -7924,7 +7264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -7945,12 +7285,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="21"/>
+      <c r="F24" s="25"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -7964,7 +7304,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -7985,7 +7325,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -8006,11 +7346,11 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="25"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -8030,7 +7370,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -8056,7 +7396,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -8082,7 +7422,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -8108,7 +7448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -8134,7 +7474,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -8155,7 +7495,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -8177,7 +7517,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -8199,7 +7539,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -8210,7 +7550,7 @@
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -8218,12 +7558,12 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="I36" s="27"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -8237,12 +7577,12 @@
       <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="21"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L37" s="25"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
@@ -8257,7 +7597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
@@ -8272,7 +7612,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
@@ -8287,7 +7627,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -8301,7 +7641,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -8315,7 +7655,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -8329,7 +7669,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -8343,7 +7683,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -8353,140 +7693,140 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="210" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="209" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="208" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="207" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="206" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="205" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="204" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="203" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="202" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="201" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="200" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="199" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="198" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="197" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="196" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="195" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="194" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="193" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="192" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="191" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="190" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="189" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="188" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="187" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="186" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="185" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="184" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="183" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="182" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="181" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="180" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="179" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="178" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="177" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="176" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="175" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="174" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="172" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="171" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="170" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8495,43 +7835,43 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A327CFEE-00BE-49D5-8C69-5CD256340320}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="2"/>
+    <col min="13" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="25"/>
+      <c r="K2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -8558,7 +7898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -8584,7 +7924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -8610,7 +7950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -8636,7 +7976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -8662,7 +8002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -8688,7 +8028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -8714,7 +8054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -8740,7 +8080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -8766,7 +8106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -8792,7 +8132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -8819,7 +8159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -8846,7 +8186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -8872,7 +8212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -8900,7 +8240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -8921,7 +8261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -8942,11 +8282,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -8959,7 +8299,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -8973,7 +8313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -8986,16 +8326,16 @@
       <c r="F21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="K21" s="21" t="s">
+      <c r="I21" s="25"/>
+      <c r="K21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="21"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L21" s="25"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -9016,7 +8356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -9037,12 +8377,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="21"/>
+      <c r="F24" s="25"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -9056,7 +8396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -9077,7 +8417,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -9098,11 +8438,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="21" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="25"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -9122,7 +8462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -9148,7 +8488,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -9174,7 +8514,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -9200,7 +8540,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -9226,7 +8566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -9247,7 +8587,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -9269,7 +8609,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -9291,7 +8631,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -9302,7 +8642,7 @@
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -9310,12 +8650,12 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="I36" s="27"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D37"/>
       <c r="H37" s="3" t="s">
         <v>37</v>
@@ -9323,12 +8663,12 @@
       <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="21"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L37" s="25"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
@@ -9343,7 +8683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
@@ -9358,7 +8698,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
@@ -9373,7 +8713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -9387,7 +8727,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -9401,7 +8741,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -9415,7 +8755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -9429,7 +8769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -9452,127 +8792,127 @@
     <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="169" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="168" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="167" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="166" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="165" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="164" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="163" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="162" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="161" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="160" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="159" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="158" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="157" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="156" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="155" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="154" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="153" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="152" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="151" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22">
-    <cfRule type="duplicateValues" dxfId="150" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="149" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="148" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="147" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="146" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="145" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="144" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="143" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="142" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="141" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="140" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="139" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="138" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="137" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="136" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="135" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="134" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="133" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="132" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="131" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="130" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="129" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9581,30 +8921,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9FC74A-71CC-442B-A4E0-26218C5C155E}">
   <dimension ref="B2:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="2"/>
+    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9619,7 +8959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -9633,7 +8973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -9647,7 +8987,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -9661,7 +9001,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -9675,7 +9015,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -9689,7 +9029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -9703,7 +9043,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -9717,7 +9057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -9731,7 +9071,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -9745,7 +9085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -9760,7 +9100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -9775,7 +9115,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -9789,7 +9129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -9804,7 +9144,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -9812,7 +9152,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="18"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
@@ -9821,11 +9161,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="21" t="s">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="25"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -9833,7 +9173,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -9847,7 +9187,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>26</v>
       </c>
@@ -9856,7 +9196,7 @@
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>34</v>
       </c>
@@ -9865,19 +9205,19 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="21"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="25"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>22</v>
       </c>
@@ -9891,7 +9231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
@@ -9905,7 +9245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>116</v>
       </c>
@@ -9919,7 +9259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>40</v>
       </c>
@@ -9933,7 +9273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="12" t="s">
         <v>78</v>
       </c>
@@ -9947,7 +9287,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="17" t="s">
         <v>118</v>
       </c>
@@ -9961,7 +9301,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E30" s="17" t="s">
         <v>115</v>
       </c>
@@ -9969,31 +9309,31 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D32"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D37"/>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D38"/>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D39"/>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D40"/>
     </row>
   </sheetData>
@@ -10004,64 +9344,64 @@
     <mergeCell ref="E23:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="128" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="127" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="126" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="125" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21 B11">
-    <cfRule type="duplicateValues" dxfId="124" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23 B18">
-    <cfRule type="duplicateValues" dxfId="123" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24 B10">
-    <cfRule type="duplicateValues" dxfId="122" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="121" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B9">
-    <cfRule type="duplicateValues" dxfId="120" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="119" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="118" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="117" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="116" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="115" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="114" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="113" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="112" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="111" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E21">
-    <cfRule type="duplicateValues" dxfId="110" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="109" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10070,70 +9410,70 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949C4FB1-0786-48FB-AC2F-6783FDA539CA}">
   <dimension ref="B2:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.44140625" style="2"/>
+    <col min="13" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="25"/>
+      <c r="H2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="25"/>
+      <c r="K2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="24" t="s">
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="21" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="L3" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -10155,11 +9495,11 @@
       <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -10175,7 +9515,7 @@
       <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -10185,7 +9525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -10207,11 +9547,11 @@
       <c r="K6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -10227,7 +9567,7 @@
       <c r="H7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="8" t="s">
@@ -10237,7 +9577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
@@ -10259,11 +9599,11 @@
       <c r="K8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
@@ -10279,7 +9619,7 @@
       <c r="H9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -10289,7 +9629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -10311,11 +9651,11 @@
       <c r="K10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -10331,7 +9671,7 @@
       <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K11" s="6" t="s">
@@ -10341,7 +9681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
@@ -10363,11 +9703,11 @@
       <c r="K12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -10384,7 +9724,7 @@
       <c r="H13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K13" s="6" t="s">
@@ -10394,7 +9734,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>118</v>
       </c>
@@ -10417,11 +9757,11 @@
       <c r="K14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="25" t="s">
+      <c r="L14" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
       <c r="E15" s="17" t="s">
         <v>110</v>
@@ -10432,7 +9772,7 @@
       <c r="H15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="22" t="s">
         <v>43</v>
       </c>
       <c r="K15" s="9" t="s">
@@ -10442,7 +9782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="E16" s="6" t="s">
         <v>35</v>
@@ -10461,15 +9801,15 @@
       <c r="K16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="25" t="s">
+      <c r="L16" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="21" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="25"/>
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -10479,7 +9819,7 @@
       <c r="H17" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J17" s="1"/>
@@ -10490,11 +9830,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="21" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -10513,11 +9853,11 @@
       <c r="K18" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="L18" s="25" t="s">
+      <c r="L18" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
         <v>30</v>
       </c>
@@ -10528,7 +9868,7 @@
       <c r="H19" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J19" s="1"/>
@@ -10539,7 +9879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="17" t="s">
         <v>115</v>
       </c>
@@ -10548,46 +9888,46 @@
       </c>
       <c r="F20" s="2"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="26"/>
+      <c r="I20" s="23"/>
       <c r="K20" s="19"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="21"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F21" s="25"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="21" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="18"/>
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="21"/>
-      <c r="K22" s="21" t="s">
+      <c r="I22" s="25"/>
+      <c r="K22" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="21"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
         <v>25</v>
       </c>
@@ -10600,20 +9940,20 @@
       <c r="F23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="24" t="s">
+      <c r="H23" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="I23" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="K23" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="27" t="s">
+      <c r="L23" s="24" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>18</v>
       </c>
@@ -10639,7 +9979,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>33</v>
       </c>
@@ -10665,7 +10005,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>96</v>
       </c>
@@ -10691,7 +10031,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C27" s="2"/>
       <c r="E27" s="6" t="s">
         <v>114</v>
@@ -10712,7 +10052,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="18"/>
       <c r="E28" s="17" t="s">
         <v>115</v>
@@ -10733,11 +10073,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="21"/>
+      <c r="C29" s="25"/>
       <c r="H29" s="11" t="s">
         <v>101</v>
       </c>
@@ -10751,11 +10091,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="24" t="s">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="21" t="s">
         <v>5</v>
       </c>
       <c r="H30" s="11" t="s">
@@ -10771,7 +10111,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>26</v>
       </c>
@@ -10791,7 +10131,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
         <v>34</v>
       </c>
@@ -10812,7 +10152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
         <v>77</v>
       </c>
@@ -10834,7 +10174,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
         <v>22</v>
       </c>
@@ -10856,7 +10196,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="6" t="s">
         <v>23</v>
       </c>
@@ -10877,7 +10217,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
         <v>116</v>
       </c>
@@ -10898,7 +10238,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="6" t="s">
         <v>40</v>
       </c>
@@ -10907,7 +10247,7 @@
       </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="12" t="s">
         <v>78</v>
       </c>
@@ -10915,16 +10255,16 @@
         <v>8</v>
       </c>
       <c r="D38"/>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="22"/>
-      <c r="K38" s="21" t="s">
+      <c r="I38" s="26"/>
+      <c r="K38" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L38" s="21"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L38" s="25"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="17" t="s">
         <v>118</v>
       </c>
@@ -10932,20 +10272,20 @@
         <v>8</v>
       </c>
       <c r="D39"/>
-      <c r="H39" s="24" t="s">
+      <c r="H39" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I39" s="24" t="s">
+      <c r="I39" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="24" t="s">
+      <c r="K39" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="24" t="s">
+      <c r="L39" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
         <v>42</v>
       </c>
@@ -10966,7 +10306,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H41" s="6" t="s">
         <v>16</v>
       </c>
@@ -10980,7 +10320,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H42" s="6" t="s">
         <v>41</v>
       </c>
@@ -10994,7 +10334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H43" s="6" t="s">
         <v>22</v>
       </c>
@@ -11008,7 +10348,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H44" s="6" t="s">
         <v>21</v>
       </c>
@@ -11022,7 +10362,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H45" s="6" t="s">
         <v>114</v>
       </c>
@@ -11036,7 +10376,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H46" s="17" t="s">
         <v>115</v>
       </c>
@@ -11200,13 +10540,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>48</v>
       </c>
@@ -11214,7 +10554,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -11222,7 +10562,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
@@ -11230,7 +10570,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
@@ -11238,7 +10578,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>21</v>
       </c>
@@ -11246,7 +10586,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -11254,7 +10594,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
@@ -11262,7 +10602,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -11270,7 +10610,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>58</v>
       </c>
@@ -11278,7 +10618,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>20</v>
       </c>
@@ -11286,7 +10626,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
@@ -11294,7 +10634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -11302,7 +10642,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>25</v>
       </c>
@@ -11310,7 +10650,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -11318,7 +10658,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
@@ -11326,7 +10666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>39</v>
       </c>
@@ -11334,7 +10674,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
@@ -11342,7 +10682,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>29</v>
       </c>
@@ -11350,7 +10690,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>40</v>
       </c>
@@ -11358,7 +10698,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
@@ -11366,7 +10706,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>33</v>
       </c>
@@ -11374,7 +10714,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>41</v>
       </c>
@@ -11382,7 +10722,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>47</v>
       </c>
@@ -11390,7 +10730,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>19</v>
       </c>
@@ -11398,7 +10738,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>35</v>
       </c>
@@ -11413,6 +10753,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -11613,36 +10968,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
-    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11665,9 +10994,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39C5F4F-6D58-4D93-9CB1-A0CAC61E4002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F548068A-AA28-4878-BBC9-01100306BBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="2" activeTab="6" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="2" activeTab="7" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
@@ -682,7 +682,437 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="267">
+  <dxfs count="310">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4570,124 +5000,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="266" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="265" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="264" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="263" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="262" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="261" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="260" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="259" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="258" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="257" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="256" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="255" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="254" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="253" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="252" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="251" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="250" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="249" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="248" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="247" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="246" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="245" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="244" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="243" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="242" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="241" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="240" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="239" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="238" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="237" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="236" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="235" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="234" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="233" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="232" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="231" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="230" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="229" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="228" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="227" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5586,127 +6016,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="226" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="225" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="224" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="223" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="222" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="221" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="220" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="219" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="218" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="217" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="216" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="215" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="214" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="213" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="212" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="211" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="210" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="209" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="208" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="207" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="205" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="204" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="203" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="202" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="201" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="200" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="199" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="198" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="197" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="196" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="194" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="193" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="192" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="191" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="190" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="189" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="188" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="187" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="186" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6151,64 +6581,64 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="185" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="184" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="183" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="182" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="181" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="180" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="179" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="178" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="177" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="176" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="175" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="174" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="173" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="172" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="171" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="170" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="169" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="168" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="167" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="166" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6679,67 +7109,67 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="165" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="164" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="163" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="162" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="161" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="160" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="159" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="158" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="157" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="156" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="155" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="154" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="153" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="152" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="151" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="150" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="149" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="148" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="147" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="146" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="145" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7693,140 +8123,140 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="144" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="143" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="142" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="141" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="140" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="139" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="138" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="137" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="136" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="135" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="134" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="133" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="132" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="131" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="130" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="129" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="128" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="127" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="126" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="125" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="124" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="123" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="122" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="121" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="120" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="119" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="118" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="117" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="116" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="115" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="114" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="113" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="112" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="111" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="110" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="109" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="108" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="107" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="106" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="105" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="104" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8792,127 +9222,127 @@
     <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="103" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="102" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="101" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="100" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="99" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="98" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="97" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="96" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="95" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="94" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="93" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="92" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="91" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="90" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="89" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="88" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="87" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="86" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="85" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22">
-    <cfRule type="duplicateValues" dxfId="84" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="83" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="81" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="79" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="78" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="76" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="74" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="73" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="72" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="71" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="70" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="69" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="66" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="65" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="64" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9344,64 +9774,64 @@
     <mergeCell ref="E23:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="62" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="60" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="59" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21 B11">
-    <cfRule type="duplicateValues" dxfId="58" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23 B18">
-    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24 B10">
-    <cfRule type="duplicateValues" dxfId="56" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="55" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B9">
-    <cfRule type="duplicateValues" dxfId="54" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="51" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="50" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E21">
-    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9409,7 +9839,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949C4FB1-0786-48FB-AC2F-6783FDA539CA}">
-  <dimension ref="B2:L46"/>
+  <dimension ref="B2:L47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
@@ -9735,12 +10165,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="1"/>
       <c r="E14" s="6" t="s">
         <v>21</v>
@@ -9783,7 +10208,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="2"/>
+      <c r="B16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="25"/>
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -9806,10 +10234,12 @@
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="25"/>
+      <c r="B17" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>5</v>
+      </c>
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -9830,12 +10260,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>5</v>
+    <row r="18" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>118</v>
@@ -9857,9 +10287,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
-        <v>30</v>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="17" t="s">
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>31</v>
@@ -9880,8 +10310,8 @@
       </c>
     </row>
     <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
-        <v>115</v>
+      <c r="B20" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>31</v>
@@ -9894,7 +10324,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>31</v>
@@ -9906,7 +10336,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>31</v>
@@ -9928,8 +10358,8 @@
       <c r="L22" s="25"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>25</v>
+      <c r="B23" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>31</v>
@@ -9955,7 +10385,7 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>31</v>
@@ -9981,7 +10411,7 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>31</v>
@@ -10006,12 +10436,7 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="C26" s="2"/>
       <c r="E26" s="6" t="s">
         <v>79</v>
       </c>
@@ -10032,7 +10457,7 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
+      <c r="B27" s="18"/>
       <c r="E27" s="6" t="s">
         <v>114</v>
       </c>
@@ -10053,7 +10478,10 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="18"/>
+      <c r="B28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="25"/>
       <c r="E28" s="17" t="s">
         <v>115</v>
       </c>
@@ -10074,10 +10502,18 @@
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="25"/>
+      <c r="B29" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="H29" s="11" t="s">
         <v>101</v>
       </c>
@@ -10092,11 +10528,11 @@
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>5</v>
+      <c r="B30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>17</v>
@@ -10112,8 +10548,8 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>26</v>
+      <c r="B31" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
@@ -10132,8 +10568,8 @@
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="16" t="s">
-        <v>34</v>
+      <c r="B32" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>14</v>
@@ -10153,8 +10589,8 @@
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
-        <v>77</v>
+      <c r="B33" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>14</v>
@@ -10176,7 +10612,7 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>14</v>
@@ -10197,11 +10633,11 @@
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
-        <v>23</v>
+      <c r="B35" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D35"/>
       <c r="H35" s="17" t="s">
@@ -10218,8 +10654,8 @@
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="8" t="s">
-        <v>116</v>
+      <c r="B36" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>8</v>
@@ -10239,82 +10675,68 @@
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
-        <v>40</v>
+      <c r="B37" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D37"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
-        <v>78</v>
+      <c r="B38" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D38"/>
-      <c r="H38" s="26" t="s">
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39"/>
+      <c r="H39" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="26"/>
-      <c r="K38" s="25" t="s">
+      <c r="I39" s="26"/>
+      <c r="K39" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L38" s="25"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39"/>
-      <c r="H39" s="21" t="s">
+      <c r="L39" s="25"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D40"/>
+      <c r="H40" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="I40" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="21" t="s">
+      <c r="K40" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="21" t="s">
+      <c r="L40" s="21" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40"/>
-      <c r="H40" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H41" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>46</v>
@@ -10322,13 +10744,13 @@
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H42" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>46</v>
@@ -10336,13 +10758,13 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H43" s="6" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>46</v>
@@ -10350,13 +10772,13 @@
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H44" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>46</v>
@@ -10364,45 +10786,59 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="H45" s="6" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H46" s="17" t="s">
-        <v>115</v>
+      <c r="H46" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K46" s="17" t="s">
-        <v>115</v>
+      <c r="K46" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="H47" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="K39:L39"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="H22:I22"/>
     <mergeCell ref="K22:L22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="42" priority="36"/>
@@ -10419,28 +10855,28 @@
   <conditionalFormatting sqref="B10">
     <cfRule type="duplicateValues" dxfId="38" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
+  <conditionalFormatting sqref="B20">
     <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
     <cfRule type="duplicateValues" dxfId="35" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31 B11">
+  <conditionalFormatting sqref="B30 B11">
     <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33 B28">
+  <conditionalFormatting sqref="B32 B27">
     <cfRule type="duplicateValues" dxfId="33" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="32" priority="37"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="30" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
@@ -10497,10 +10933,10 @@
   <conditionalFormatting sqref="H34">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H43">
+  <conditionalFormatting sqref="H44">
     <cfRule type="duplicateValues" dxfId="11" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
+  <conditionalFormatting sqref="H45">
     <cfRule type="duplicateValues" dxfId="10" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
@@ -10527,10 +10963,10 @@
   <conditionalFormatting sqref="K34">
     <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
+  <conditionalFormatting sqref="K44">
     <cfRule type="duplicateValues" dxfId="1" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+  <conditionalFormatting sqref="K45">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10753,21 +11189,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -10968,10 +11389,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10994,20 +11441,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
-    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F548068A-AA28-4878-BBC9-01100306BBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B862B-241D-46D1-A916-72627197C19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="2" activeTab="7" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="119">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -669,10 +669,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -682,377 +682,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="310">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="273">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4132,23 +3762,23 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="H3" s="25" t="s">
+      <c r="F3" s="26"/>
+      <c r="H3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="25"/>
-      <c r="K3" s="25" t="s">
+      <c r="I3" s="26"/>
+      <c r="K3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="25"/>
+      <c r="L3" s="26"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -4535,10 +4165,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
@@ -4559,14 +4189,14 @@
       <c r="F20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="25" t="s">
+      <c r="H20" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="25"/>
-      <c r="K20" s="25" t="s">
+      <c r="I20" s="26"/>
+      <c r="K20" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="25"/>
+      <c r="L20" s="26"/>
     </row>
     <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
@@ -4611,10 +4241,10 @@
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="25"/>
+      <c r="F23" s="26"/>
       <c r="H23" s="11" t="s">
         <v>16</v>
       </c>
@@ -4629,10 +4259,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
@@ -4876,14 +4506,14 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="25" t="s">
         <v>44</v>
       </c>
       <c r="I35" s="27"/>
-      <c r="K35" s="25" t="s">
+      <c r="K35" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L35" s="25"/>
+      <c r="L35" s="26"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="6" t="s">
@@ -5000,124 +4630,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="309" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="308" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="307" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="306" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="305" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="304" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="303" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="302" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="301" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="300" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="299" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="298" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="297" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="296" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="295" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="294" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="293" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="292" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="291" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="290" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="289" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="288" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="287" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="286" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="285" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="284" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="283" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="282" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="281" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="280" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="279" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="278" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="277" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="276" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="275" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="274" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="273" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="272" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="271" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="270" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5144,23 +4774,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="F2" s="26"/>
+      <c r="H2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="I2" s="26"/>
+      <c r="K2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -5547,10 +5177,10 @@
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="25"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -5571,14 +5201,14 @@
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="K19" s="25" t="s">
+      <c r="I19" s="26"/>
+      <c r="K19" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="25"/>
+      <c r="L19" s="26"/>
     </row>
     <row r="20" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
@@ -5687,10 +5317,10 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="25"/>
+      <c r="F25" s="26"/>
       <c r="H25" s="11" t="s">
         <v>20</v>
       </c>
@@ -5705,10 +5335,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="25"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
@@ -5892,14 +5522,14 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="26" t="s">
+      <c r="H34" s="25" t="s">
         <v>44</v>
       </c>
       <c r="I34" s="27"/>
-      <c r="K34" s="25" t="s">
+      <c r="K34" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="25"/>
+      <c r="L34" s="26"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
@@ -6016,127 +5646,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="269" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="268" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="267" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="266" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="265" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="264" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="263" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="262" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="261" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="260" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="259" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="258" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="257" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="256" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="255" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="254" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="253" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="252" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="251" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="250" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="249" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="248" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="247" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="246" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="245" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="244" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="243" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="242" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="241" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="240" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="239" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="238" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="237" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="236" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="235" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="234" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="233" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="232" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="231" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="230" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="229" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6158,15 +5788,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -6371,10 +6001,10 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="25"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -6419,10 +6049,10 @@
       <c r="E22" s="18"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="25"/>
+      <c r="C23" s="26"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
@@ -6432,10 +6062,10 @@
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="25"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
@@ -6581,64 +6211,64 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="228" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="227" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="226" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="225" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="224" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="223" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="222" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="221" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="220" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="219" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="218" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="217" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="216" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="215" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="214" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="213" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="212" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="211" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="210" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="209" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6665,15 +6295,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -6892,10 +6522,10 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -6946,10 +6576,10 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="25"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="18"/>
@@ -6970,10 +6600,10 @@
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="25"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -7109,67 +6739,67 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="208" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="207" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="206" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="205" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="204" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="203" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="202" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="201" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="200" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="199" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="198" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="197" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="196" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="194" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="193" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="192" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="191" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="190" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="189" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="188" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7196,23 +6826,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="F2" s="26"/>
+      <c r="H2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="I2" s="26"/>
+      <c r="K2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -7626,10 +7256,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -7664,14 +7294,14 @@
         <v>32</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="25"/>
-      <c r="K21" s="25" t="s">
+      <c r="I21" s="26"/>
+      <c r="K21" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="25"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
@@ -7717,10 +7347,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="25"/>
+      <c r="F24" s="26"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -7777,10 +7407,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="25"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -7988,7 +7618,7 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="26" t="s">
+      <c r="H36" s="25" t="s">
         <v>44</v>
       </c>
       <c r="I36" s="27"/>
@@ -8007,10 +7637,10 @@
       <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="25" t="s">
+      <c r="K37" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="25"/>
+      <c r="L37" s="26"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
@@ -8123,140 +7753,140 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="187" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="186" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="185" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="184" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="183" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="182" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="181" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="180" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="179" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="178" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="177" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="176" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="175" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="174" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="173" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="172" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="171" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="170" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="169" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="168" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="167" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="166" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="165" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="164" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="163" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="162" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="161" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="160" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="159" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="158" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="157" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="156" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="155" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="154" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="153" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="152" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="151" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="150" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="149" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="148" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="147" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8283,23 +7913,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="F2" s="26"/>
+      <c r="H2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="I2" s="26"/>
+      <c r="K2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -8713,10 +8343,10 @@
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -8756,14 +8386,14 @@
       <c r="F21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="25"/>
-      <c r="K21" s="25" t="s">
+      <c r="I21" s="26"/>
+      <c r="K21" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="25"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
@@ -8809,10 +8439,10 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="18"/>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="25"/>
+      <c r="F24" s="26"/>
       <c r="H24" s="11" t="s">
         <v>16</v>
       </c>
@@ -8869,10 +8499,10 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="25"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
@@ -9080,7 +8710,7 @@
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="H36" s="26" t="s">
+      <c r="H36" s="25" t="s">
         <v>44</v>
       </c>
       <c r="I36" s="27"/>
@@ -9093,10 +8723,10 @@
       <c r="I37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K37" s="25" t="s">
+      <c r="K37" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L37" s="25"/>
+      <c r="L37" s="26"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D38"/>
@@ -9222,127 +8852,127 @@
     <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="146" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="145" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="144" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="143" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="142" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="141" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="140" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="139" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="138" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="137" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="136" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="135" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="134" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="133" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="132" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="131" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="130" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="129" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="128" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22">
-    <cfRule type="duplicateValues" dxfId="127" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="126" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="125" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="124" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="123" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="122" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="121" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="120" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="119" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="118" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="117" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="116" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="115" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="114" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="113" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="112" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="111" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="110" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="109" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="108" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="107" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="106" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9364,15 +8994,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -9592,10 +9222,10 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="25"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="8" t="s">
         <v>33</v>
       </c>
@@ -9642,10 +9272,10 @@
       <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="25"/>
+      <c r="F23" s="26"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
@@ -9774,64 +9404,64 @@
     <mergeCell ref="E23:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="105" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="104" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="103" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="102" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21 B11">
-    <cfRule type="duplicateValues" dxfId="101" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23 B18">
-    <cfRule type="duplicateValues" dxfId="100" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24 B10">
-    <cfRule type="duplicateValues" dxfId="99" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="98" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B9">
-    <cfRule type="duplicateValues" dxfId="97" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="96" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="95" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="94" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="93" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="92" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="91" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="89" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E21">
-    <cfRule type="duplicateValues" dxfId="87" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9858,23 +9488,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="H2" s="25" t="s">
+      <c r="F2" s="26"/>
+      <c r="H2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="I2" s="26"/>
+      <c r="K2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
@@ -10165,7 +9795,12 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
+      <c r="B14" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="6" t="s">
         <v>21</v>
@@ -10208,10 +9843,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -10329,10 +9964,10 @@
       <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="25"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
@@ -10348,14 +9983,14 @@
         <v>5</v>
       </c>
       <c r="G22" s="18"/>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="25"/>
-      <c r="K22" s="25" t="s">
+      <c r="I22" s="26"/>
+      <c r="K22" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="25"/>
+      <c r="L22" s="26"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
@@ -10478,10 +10113,10 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="25"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="17" t="s">
         <v>115</v>
       </c>
@@ -10704,14 +10339,14 @@
         <v>43</v>
       </c>
       <c r="D39"/>
-      <c r="H39" s="26" t="s">
+      <c r="H39" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="K39" s="25" t="s">
+      <c r="I39" s="25"/>
+      <c r="K39" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L39" s="25"/>
+      <c r="L39" s="26"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D40"/>
@@ -10840,134 +10475,137 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="42" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="40" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B27">
+    <cfRule type="duplicateValues" dxfId="39" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="37" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="30" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="29" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="28" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26">
+    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="duplicateValues" dxfId="26" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29:H30">
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H44">
+    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45">
+    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28">
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K29:K30">
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34">
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44">
+    <cfRule type="duplicateValues" dxfId="7" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="duplicateValues" dxfId="6" priority="28"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="42" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="41" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="38" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B11">
-    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32 B27">
-    <cfRule type="duplicateValues" dxfId="33" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="30" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
-    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="duplicateValues" dxfId="20" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H30">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
-    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H45">
-    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K28">
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K29:K30">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
-    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11189,6 +10827,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -11389,36 +11042,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
-    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11441,9 +11068,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Octubre.xlsx
+++ b/Cronograma de Tareas/Cronograma Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B862B-241D-46D1-A916-72627197C19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="816" firstSheet="2" activeTab="7" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="816" firstSheet="3" activeTab="7" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 28 Sep al 04 de Oct" sheetId="24" r:id="rId1"/>
@@ -682,57 +682,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="273">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="268">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3744,24 +3694,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AC30FF-4C9E-4211-B41D-FEC83E8B88B1}">
   <dimension ref="B3:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
@@ -3780,7 +3730,7 @@
       </c>
       <c r="L3" s="26"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3807,7 +3757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -3833,7 +3783,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
@@ -3859,7 +3809,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
@@ -3885,7 +3835,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
@@ -3911,7 +3861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
@@ -3937,7 +3887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
@@ -3963,7 +3913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
@@ -3989,7 +3939,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>29</v>
       </c>
@@ -4015,7 +3965,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>35</v>
       </c>
@@ -4041,7 +3991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>102</v>
       </c>
@@ -4068,7 +4018,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
         <v>104</v>
       </c>
@@ -4095,7 +4045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>95</v>
       </c>
@@ -4121,7 +4071,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
@@ -4143,7 +4093,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E18" s="6" t="s">
         <v>25</v>
       </c>
@@ -4164,7 +4114,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
@@ -4176,7 +4126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -4198,7 +4148,7 @@
       </c>
       <c r="L20" s="26"/>
     </row>
-    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -4224,7 +4174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="18"/>
       <c r="F22" s="2"/>
       <c r="H22" s="11" t="s">
@@ -4240,7 +4190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E23" s="26" t="s">
         <v>89</v>
       </c>
@@ -4258,7 +4208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="26" t="s">
         <v>36</v>
       </c>
@@ -4282,7 +4232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
@@ -4308,7 +4258,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
@@ -4334,7 +4284,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="16" t="s">
         <v>34</v>
       </c>
@@ -4360,7 +4310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>77</v>
       </c>
@@ -4386,7 +4336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>22</v>
       </c>
@@ -4406,7 +4356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
@@ -4426,7 +4376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>40</v>
       </c>
@@ -4446,7 +4396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>39</v>
       </c>
@@ -4467,7 +4417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
         <v>78</v>
       </c>
@@ -4489,7 +4439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -4498,7 +4448,7 @@
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -4515,7 +4465,7 @@
       </c>
       <c r="L35" s="26"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>42</v>
       </c>
@@ -4536,7 +4486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>12</v>
@@ -4551,7 +4501,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>16</v>
@@ -4566,7 +4516,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>41</v>
@@ -4581,7 +4531,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>22</v>
@@ -4596,7 +4546,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D41"/>
       <c r="H41" s="6" t="s">
         <v>21</v>
@@ -4611,7 +4561,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D42"/>
     </row>
   </sheetData>
@@ -4630,124 +4580,124 @@
     <mergeCell ref="K20:L20"/>
   </mergeCells>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="272" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="271" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="270" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B13">
-    <cfRule type="duplicateValues" dxfId="269" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B22">
-    <cfRule type="duplicateValues" dxfId="268" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="267" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="266" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B26 B12">
-    <cfRule type="duplicateValues" dxfId="265" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="264" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="263" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="262" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="261" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="260" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="259" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="258" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="257" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="duplicateValues" dxfId="256" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="duplicateValues" dxfId="255" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="254" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="253" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="252" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="251" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="250" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="249" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="248" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="duplicateValues" dxfId="247" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:H28">
-    <cfRule type="duplicateValues" dxfId="246" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="duplicateValues" dxfId="245" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="244" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="243" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5">
-    <cfRule type="duplicateValues" dxfId="242" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="241" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="240" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="duplicateValues" dxfId="239" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="duplicateValues" dxfId="238" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="237" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:K28">
-    <cfRule type="duplicateValues" dxfId="236" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="duplicateValues" dxfId="235" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="234" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="duplicateValues" dxfId="233" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="17"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4756,24 +4706,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D300C407-A034-411B-B7F2-D7830F6D8BD1}">
   <dimension ref="B2:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="4" max="4" width="11.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -4792,7 +4742,7 @@
       </c>
       <c r="L2" s="26"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -4819,7 +4769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4845,7 +4795,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -4871,7 +4821,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -4897,7 +4847,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -4923,7 +4873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -4949,7 +4899,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -4975,7 +4925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5001,7 +4951,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -5027,7 +4977,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5053,7 +5003,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>94</v>
       </c>
@@ -5080,7 +5030,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
@@ -5107,7 +5057,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -5133,7 +5083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -5155,7 +5105,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -5176,7 +5126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
         <v>24</v>
       </c>
@@ -5188,7 +5138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -5210,7 +5160,7 @@
       </c>
       <c r="L19" s="26"/>
     </row>
-    <row r="20" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -5236,7 +5186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>111</v>
       </c>
@@ -5262,7 +5212,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>112</v>
       </c>
@@ -5283,7 +5233,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="18"/>
       <c r="E23" s="18"/>
       <c r="H23" s="11" t="s">
@@ -5299,7 +5249,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="F24" s="2"/>
       <c r="H24" s="11" t="s">
@@ -5315,7 +5265,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
       <c r="E25" s="26" t="s">
         <v>89</v>
@@ -5334,7 +5284,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="26" t="s">
         <v>36</v>
       </c>
@@ -5358,7 +5308,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>4</v>
       </c>
@@ -5384,7 +5334,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>26</v>
       </c>
@@ -5410,7 +5360,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>34</v>
       </c>
@@ -5436,7 +5386,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>77</v>
       </c>
@@ -5462,7 +5412,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
@@ -5483,7 +5433,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
@@ -5505,7 +5455,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>40</v>
       </c>
@@ -5514,7 +5464,7 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
@@ -5531,7 +5481,7 @@
       </c>
       <c r="L34" s="26"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
@@ -5552,7 +5502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -5567,7 +5517,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -5582,7 +5532,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>41</v>
@@ -5597,7 +5547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -5612,7 +5562,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>21</v>
@@ -5627,7 +5577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D41"/>
     </row>
   </sheetData>
@@ -5646,127 +5596,127 @@
     <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="232" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="231" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="230" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="229" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="228" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B11">
-    <cfRule type="duplicateValues" dxfId="227" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B22:B25">
-    <cfRule type="duplicateValues" dxfId="226" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B10">
-    <cfRule type="duplicateValues" dxfId="225" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="224" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="223" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="222" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="221" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="220" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="219" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="218" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="217" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="216" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="215" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="214" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22:E23">
-    <cfRule type="duplicateValues" dxfId="213" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="duplicateValues" dxfId="212" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="211" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="210" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="209" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="208" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="207" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="206" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="205" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="204" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="203" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="202" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="201" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="200" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="199" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="198" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="197" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="196" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="195" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="194" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="193" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="192" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5775,19 +5725,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86259B90-4A78-45A3-AC3D-5D90B4EC10BE}">
   <dimension ref="B2:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="86.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="86.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5703125" style="2"/>
+    <col min="4" max="4" width="6.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -5798,7 +5748,7 @@
       </c>
       <c r="F2" s="26"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -5813,7 +5763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5827,7 +5777,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5841,7 +5791,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -5855,7 +5805,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -5869,7 +5819,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -5883,7 +5833,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5897,7 +5847,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5911,7 +5861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -5925,7 +5875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5939,7 +5889,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -5954,7 +5904,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -5969,7 +5919,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -5983,7 +5933,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
@@ -5992,7 +5942,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -6000,7 +5950,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
         <v>24</v>
       </c>
@@ -6012,7 +5962,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
@@ -6026,7 +5976,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>30</v>
       </c>
@@ -6040,22 +5990,22 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="18"/>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="18"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="26" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="26"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
@@ -6067,7 +6017,7 @@
       </c>
       <c r="F24" s="26"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>26</v>
       </c>
@@ -6081,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
         <v>34</v>
       </c>
@@ -6095,7 +6045,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
         <v>77</v>
       </c>
@@ -6109,7 +6059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
@@ -6123,7 +6073,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>23</v>
       </c>
@@ -6137,7 +6087,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>40</v>
       </c>
@@ -6151,7 +6101,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>39</v>
       </c>
@@ -6159,7 +6109,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
         <v>78</v>
       </c>
@@ -6168,7 +6118,7 @@
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
@@ -6177,28 +6127,28 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D35"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D36"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D37"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D40"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D41"/>
     </row>
   </sheetData>
@@ -6211,64 +6161,64 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="191" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="190" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="189" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B12">
-    <cfRule type="duplicateValues" dxfId="188" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B11">
-    <cfRule type="duplicateValues" dxfId="187" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B21:B22">
-    <cfRule type="duplicateValues" dxfId="186" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B10">
-    <cfRule type="duplicateValues" dxfId="185" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30 B9">
-    <cfRule type="duplicateValues" dxfId="184" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="183" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="182" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="181" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="180" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="179" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="178" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="177" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="176" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="175" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="174" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="173" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="172" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6277,24 +6227,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF5651-411C-4D6B-9CDC-2649BAF989E6}">
   <dimension ref="B2:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -6305,7 +6255,7 @@
       </c>
       <c r="F2" s="26"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6320,7 +6270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -6334,7 +6284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -6348,7 +6298,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -6362,7 +6312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -6376,7 +6326,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -6390,7 +6340,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -6404,7 +6354,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -6418,7 +6368,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -6432,7 +6382,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -6446,7 +6396,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -6461,7 +6411,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -6476,7 +6426,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -6490,7 +6440,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -6505,7 +6455,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -6513,7 +6463,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -6521,7 +6471,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
@@ -6533,7 +6483,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -6547,7 +6497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -6556,7 +6506,7 @@
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -6565,7 +6515,7 @@
       </c>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -6574,14 +6524,14 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="E24" s="26" t="s">
         <v>89</v>
       </c>
       <c r="F24" s="26"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -6590,7 +6540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -6599,7 +6549,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
@@ -6611,7 +6561,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -6625,7 +6575,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -6639,7 +6589,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -6653,7 +6603,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -6667,7 +6617,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -6676,7 +6626,7 @@
       </c>
       <c r="D32"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -6685,7 +6635,7 @@
       </c>
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -6694,7 +6644,7 @@
       </c>
       <c r="D34"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -6703,7 +6653,7 @@
       </c>
       <c r="D35"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -6712,7 +6662,7 @@
       </c>
       <c r="D36"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -6721,13 +6671,13 @@
       </c>
       <c r="D37"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D40"/>
     </row>
   </sheetData>
@@ -6739,67 +6689,67 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="171" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="170" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="169" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="168" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="167" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="166" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="165" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="164" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="163" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="162" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="161" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="160" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="159" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="158" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="157" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="156" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="155" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="154" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="153" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="152" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="151" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6808,24 +6758,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA997E6-02B4-4928-B7AA-4641419D4CD9}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -6844,7 +6794,7 @@
       </c>
       <c r="L2" s="26"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -6871,7 +6821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -6897,7 +6847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -6923,7 +6873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -6949,7 +6899,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -6975,7 +6925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -7001,7 +6951,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -7027,7 +6977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -7053,7 +7003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -7079,7 +7029,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -7105,7 +7055,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -7132,7 +7082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -7159,7 +7109,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -7185,7 +7135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -7213,7 +7163,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -7234,7 +7184,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -7255,7 +7205,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
@@ -7272,7 +7222,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -7286,7 +7236,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -7303,7 +7253,7 @@
       </c>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -7324,7 +7274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -7345,7 +7295,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="E24" s="26" t="s">
         <v>89</v>
@@ -7364,7 +7314,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -7385,7 +7335,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -7406,7 +7356,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
@@ -7430,7 +7380,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -7456,7 +7406,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -7482,7 +7432,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -7508,7 +7458,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -7534,7 +7484,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -7555,7 +7505,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -7577,7 +7527,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -7599,7 +7549,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -7610,7 +7560,7 @@
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -7623,7 +7573,7 @@
       </c>
       <c r="I36" s="27"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>42</v>
       </c>
@@ -7642,7 +7592,7 @@
       </c>
       <c r="L37" s="26"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
@@ -7657,7 +7607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
@@ -7672,7 +7622,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
@@ -7687,7 +7637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -7701,7 +7651,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -7715,7 +7665,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -7729,7 +7679,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -7743,7 +7693,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -7753,140 +7703,140 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="150" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="149" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="148" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="147" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="146" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="145" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="144" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="143" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="142" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="141" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="140" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="139" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="138" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="137" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="136" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="135" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="134" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="133" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="132" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E22">
-    <cfRule type="duplicateValues" dxfId="131" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="130" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="129" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="128" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="127" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="126" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="125" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="124" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="123" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="122" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="121" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="120" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="119" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="118" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="117" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="116" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="115" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="114" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="113" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="112" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="111" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="110" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7895,24 +7845,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A327CFEE-00BE-49D5-8C69-5CD256340320}">
   <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.5703125" style="2"/>
+    <col min="13" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -7931,7 +7881,7 @@
       </c>
       <c r="L2" s="26"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -7958,7 +7908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -7984,7 +7934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -8010,7 +7960,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -8036,7 +7986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -8062,7 +8012,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -8088,7 +8038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -8114,7 +8064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -8140,7 +8090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -8166,7 +8116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -8192,7 +8142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -8219,7 +8169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -8246,7 +8196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -8272,7 +8222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -8300,7 +8250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -8321,7 +8271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
@@ -8342,7 +8292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>24</v>
       </c>
@@ -8359,7 +8309,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -8373,7 +8323,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>30</v>
       </c>
@@ -8395,7 +8345,7 @@
       </c>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
@@ -8416,7 +8366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>117</v>
       </c>
@@ -8437,7 +8387,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="18"/>
       <c r="E24" s="26" t="s">
         <v>89</v>
@@ -8456,7 +8406,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="18"/>
       <c r="E25" s="3" t="s">
         <v>37</v>
@@ -8477,7 +8427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="18"/>
       <c r="E26" s="6" t="s">
         <v>12</v>
@@ -8498,7 +8448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="26" t="s">
         <v>36</v>
       </c>
@@ -8522,7 +8472,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -8548,7 +8498,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>26</v>
       </c>
@@ -8574,7 +8524,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>34</v>
       </c>
@@ -8600,7 +8550,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>77</v>
       </c>
@@ -8626,7 +8576,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -8647,7 +8597,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>23</v>
       </c>
@@ -8669,7 +8619,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
         <v>116</v>
       </c>
@@ -8691,7 +8641,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>40</v>
       </c>
@@ -8702,7 +8652,7 @@
       <c r="K35" s="19"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>78</v>
       </c>
@@ -8715,7 +8665,7 @@
       </c>
       <c r="I36" s="27"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D37"/>
       <c r="H37" s="3" t="s">
         <v>37</v>
@@ -8728,7 +8678,7 @@
       </c>
       <c r="L37" s="26"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>12</v>
@@ -8743,7 +8693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>16</v>
@@ -8758,7 +8708,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="6" t="s">
         <v>41</v>
@@ -8773,7 +8723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H41" s="6" t="s">
         <v>22</v>
       </c>
@@ -8787,7 +8737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H42" s="6" t="s">
         <v>21</v>
       </c>
@@ -8801,7 +8751,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H43" s="6" t="s">
         <v>114</v>
       </c>
@@ -8815,7 +8765,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H44" s="17" t="s">
         <v>115</v>
       </c>
@@ -8829,7 +8779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K45" s="17" t="s">
         <v>115</v>
       </c>
@@ -8852,127 +8802,127 @@
     <mergeCell ref="K21:L21"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="109" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="108" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="107" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="106" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="105" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29 B11">
-    <cfRule type="duplicateValues" dxfId="104" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B23:B26">
-    <cfRule type="duplicateValues" dxfId="103" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="102" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="101" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B9">
-    <cfRule type="duplicateValues" dxfId="100" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="99" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="98" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="97" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="96" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="95" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="94" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="93" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="92" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="91" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E22">
-    <cfRule type="duplicateValues" dxfId="90" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="89" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="88" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="87" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="86" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="85" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H29">
-    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41">
-    <cfRule type="duplicateValues" dxfId="80" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="79" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="77" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="76" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="75" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="74" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="73" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K29">
-    <cfRule type="duplicateValues" dxfId="72" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="duplicateValues" dxfId="70" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="duplicateValues" dxfId="69" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8981,19 +8931,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9FC74A-71CC-442B-A4E0-26218C5C155E}">
   <dimension ref="B2:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="11.5703125" style="2"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -9004,7 +8954,7 @@
       </c>
       <c r="F2" s="26"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9019,7 +8969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -9033,7 +8983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -9047,7 +8997,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -9061,7 +9011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -9075,7 +9025,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -9089,7 +9039,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -9103,7 +9053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -9117,7 +9067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -9131,7 +9081,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -9145,7 +9095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
@@ -9160,7 +9110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
@@ -9175,7 +9125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
@@ -9189,7 +9139,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>115</v>
       </c>
@@ -9204,7 +9154,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E17" s="6" t="s">
         <v>25</v>
       </c>
@@ -9212,7 +9162,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="18"/>
       <c r="E18" s="8" t="s">
         <v>18</v>
@@ -9221,7 +9171,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>36</v>
       </c>
@@ -9233,7 +9183,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
@@ -9247,7 +9197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>26</v>
       </c>
@@ -9256,7 +9206,7 @@
       </c>
       <c r="E21" s="18"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
         <v>34</v>
       </c>
@@ -9265,7 +9215,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>77</v>
       </c>
@@ -9277,7 +9227,7 @@
       </c>
       <c r="F23" s="26"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>22</v>
       </c>
@@ -9291,7 +9241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
@@ -9305,7 +9255,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>116</v>
       </c>
@@ -9319,7 +9269,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>40</v>
       </c>
@@ -9333,7 +9283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
         <v>78</v>
       </c>
@@ -9347,7 +9297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="17" t="s">
         <v>118</v>
       </c>
@@ -9361,7 +9311,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="E30" s="17" t="s">
         <v>115</v>
       </c>
@@ -9369,31 +9319,31 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D32"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33"/>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34"/>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35"/>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36"/>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37"/>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D40"/>
     </row>
   </sheetData>
@@ -9404,64 +9354,64 @@
     <mergeCell ref="E23:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="68" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="66" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17 B12">
-    <cfRule type="duplicateValues" dxfId="65" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21 B11">
-    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23 B18">
-    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24 B10">
-    <cfRule type="duplicateValues" dxfId="62" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B9">
-    <cfRule type="duplicateValues" dxfId="60" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="59" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="58" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="57" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="55" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="53" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20:E21">
-    <cfRule type="duplicateValues" dxfId="50" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28">
-    <cfRule type="duplicateValues" dxfId="49" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9470,24 +9420,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949C4FB1-0786-48FB-AC2F-6783FDA539CA}">
   <dimension ref="B2:L47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="87.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="65.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="65.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="2"/>
+    <col min="13" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
@@ -9506,7 +9456,7 @@
       </c>
       <c r="L2" s="26"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>4</v>
       </c>
@@ -9533,7 +9483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -9559,7 +9509,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -9585,7 +9535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -9611,7 +9561,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -9637,7 +9587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
@@ -9663,7 +9613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
@@ -9689,7 +9639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -9715,7 +9665,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
@@ -9741,7 +9691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
@@ -9767,7 +9717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -9794,7 +9744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>110</v>
       </c>
@@ -9821,7 +9771,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C15" s="2"/>
       <c r="E15" s="17" t="s">
         <v>110</v>
@@ -9842,7 +9792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
         <v>24</v>
       </c>
@@ -9868,7 +9818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="21" t="s">
         <v>4</v>
       </c>
@@ -9895,7 +9845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
@@ -9922,7 +9872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="17" t="s">
         <v>115</v>
       </c>
@@ -9944,7 +9894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
@@ -9957,7 +9907,7 @@
       <c r="K20" s="19"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
@@ -9969,7 +9919,7 @@
       </c>
       <c r="F21" s="26"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>25</v>
       </c>
@@ -9992,7 +9942,7 @@
       </c>
       <c r="L22" s="26"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
@@ -10018,7 +9968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="8" t="s">
         <v>33</v>
       </c>
@@ -10044,7 +9994,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>96</v>
       </c>
@@ -10070,7 +10020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C26" s="2"/>
       <c r="E26" s="6" t="s">
         <v>79</v>
@@ -10091,7 +10041,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="18"/>
       <c r="E27" s="6" t="s">
         <v>114</v>
@@ -10112,7 +10062,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="26" t="s">
         <v>36</v>
       </c>
@@ -10136,7 +10086,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="21" t="s">
         <v>4</v>
       </c>
@@ -10162,7 +10112,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>26</v>
       </c>
@@ -10182,7 +10132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
         <v>34</v>
       </c>
@@ -10202,7 +10152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>77</v>
       </c>
@@ -10223,7 +10173,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
@@ -10245,7 +10195,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>23</v>
       </c>
@@ -10267,7 +10217,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>116</v>
       </c>
@@ -10288,7 +10238,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>40</v>
       </c>
@@ -10309,7 +10259,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="12" t="s">
         <v>78</v>
       </c>
@@ -10322,7 +10272,7 @@
       <c r="K37" s="19"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="17" t="s">
         <v>118</v>
       </c>
@@ -10331,7 +10281,7 @@
       </c>
       <c r="D38"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>42</v>
       </c>
@@ -10348,7 +10298,7 @@
       </c>
       <c r="L39" s="26"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D40"/>
       <c r="H40" s="21" t="s">
         <v>37</v>
@@ -10363,7 +10313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H41" s="6" t="s">
         <v>12</v>
       </c>
@@ -10377,7 +10327,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H42" s="6" t="s">
         <v>16</v>
       </c>
@@ -10391,7 +10341,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H43" s="6" t="s">
         <v>41</v>
       </c>
@@ -10405,7 +10355,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H44" s="6" t="s">
         <v>22</v>
       </c>
@@ -10419,7 +10369,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H45" s="6" t="s">
         <v>21</v>
       </c>
@@ -10433,7 +10383,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H46" s="6" t="s">
         <v>114</v>
       </c>
@@ -10447,7 +10397,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H47" s="17" t="s">
         <v>115</v>
       </c>
@@ -10475,137 +10425,137 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="duplicateValues" dxfId="40" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="38" priority="6"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="42" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="40" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B27">
-    <cfRule type="duplicateValues" dxfId="39" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="37" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="36" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="32" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="30" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="29" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="28" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26">
-    <cfRule type="duplicateValues" dxfId="27" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22">
-    <cfRule type="duplicateValues" dxfId="26" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:H30">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34">
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45">
-    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29:K30">
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44">
-    <cfRule type="duplicateValues" dxfId="7" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45">
-    <cfRule type="duplicateValues" dxfId="6" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10614,13 +10564,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="95.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="95.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="94.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>48</v>
       </c>
@@ -10628,7 +10578,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -10636,7 +10586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
@@ -10644,7 +10594,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
@@ -10652,7 +10602,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>21</v>
       </c>
@@ -10660,7 +10610,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -10668,7 +10618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
@@ -10676,7 +10626,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
@@ -10684,7 +10634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>58</v>
       </c>
@@ -10692,7 +10642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>20</v>
       </c>
@@ -10700,7 +10650,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
@@ -10708,7 +10658,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -10716,7 +10666,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>25</v>
       </c>
@@ -10724,7 +10674,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -10732,7 +10682,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
@@ -10740,7 +10690,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>39</v>
       </c>
@@ -10748,7 +10698,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>42</v>
       </c>
@@ -10756,7 +10706,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>29</v>
       </c>
@@ -10764,7 +10714,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>40</v>
       </c>
@@ -10772,7 +10722,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
@@ -10780,7 +10730,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>33</v>
       </c>
@@ -10788,7 +10738,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>41</v>
       </c>
@@ -10796,7 +10746,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>47</v>
       </c>
@@ -10804,7 +10754,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>19</v>
       </c>
@@ -10812,7 +10762,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>35</v>
       </c>
@@ -10827,21 +10777,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -11042,10 +10977,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
+    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11068,20 +11029,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
-    <ds:schemaRef ds:uri="fc5c7554-ce1a-493c-be4c-f5f61635795a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>